--- a/Radiative_Transfer_Lab.xlsx
+++ b/Radiative_Transfer_Lab.xlsx
@@ -9,16 +9,16 @@
   </bookViews>
   <sheets>
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="L1 Optical depth" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="L2 Intensity" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="L3 Planck" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="L4 Random walk" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="L5 Slab &amp; MIT star" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="L6 Saha-Boltzmann" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="L7 Eddington-Barbier" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="L8 Scattering" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="L9 Gray atmosphere" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="L10 Lines" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="RT1 Optical depth" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="RT2 Intensity" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="RT3 Planck" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RT4 Random walk" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RT5 Slab &amp; MIT star" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="SA1 Saha-Boltzmann" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="RT7 Eddington-Barbier" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="RT8 Scattering" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="SA5 Gray atmosphere" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="SA6 Lines" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Constants" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Data" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
@@ -541,61 +541,61 @@
     <t xml:space="preserve">Sheets</t>
   </si>
   <si>
-    <t xml:space="preserve">L1 Optical depth</t>
+    <t xml:space="preserve">RT1 Optical depth</t>
   </si>
   <si>
     <t xml:space="preserve">Beam attenuation, optical depth, magnitudes of extinction</t>
   </si>
   <si>
-    <t xml:space="preserve">L2 Intensity</t>
+    <t xml:space="preserve">RT2 Intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Flux falls as 1/d^2, solid angle too: intensity is conserved</t>
   </si>
   <si>
-    <t xml:space="preserve">L3 Planck</t>
+    <t xml:space="preserve">RT3 Planck</t>
   </si>
   <si>
     <t xml:space="preserve">Black-body spectrum, Wien peak, Stefan-Boltzmann, RJ and Wien limits</t>
   </si>
   <si>
-    <t xml:space="preserve">L4 Random walk</t>
+    <t xml:space="preserve">RT4 Random walk</t>
   </si>
   <si>
     <t xml:space="preserve">Mean free path, photon diffusion time, thermalisation depth</t>
   </si>
   <si>
-    <t xml:space="preserve">L5 Slab &amp; MIT star</t>
+    <t xml:space="preserve">RT5 Slab &amp; MIT star</t>
   </si>
   <si>
     <t xml:space="preserve">Slab solution; MIT two-layer star with Balmer + Paschen lines; thermal inversion</t>
   </si>
   <si>
-    <t xml:space="preserve">L6 Saha-Boltzmann</t>
+    <t xml:space="preserve">SA1 Saha-Boltzmann</t>
   </si>
   <si>
     <t xml:space="preserve">Hydrogen ionisation and n=2 population; why Balmer lines peak in A stars</t>
   </si>
   <si>
-    <t xml:space="preserve">L7 Eddington-Barbier</t>
+    <t xml:space="preserve">RT7 Eddington-Barbier</t>
   </si>
   <si>
     <t xml:space="preserve">Emergent intensity, limb darkening, Eddington-Barbier error</t>
   </si>
   <si>
-    <t xml:space="preserve">L8 Scattering</t>
+    <t xml:space="preserve">RT8 Scattering</t>
   </si>
   <si>
     <t xml:space="preserve">S = eps B + (1-eps) J: Eddington solution, sqrt(eps) law; Rosseland mean calculator</t>
   </si>
   <si>
-    <t xml:space="preserve">L9 Gray atmosphere</t>
+    <t xml:space="preserve">SA5 Gray atmosphere</t>
   </si>
   <si>
     <t xml:space="preserve">Exact gray LTE model: T(tau), limb darkening at any wavelength, emergent spectrum, pressure</t>
   </si>
   <si>
-    <t xml:space="preserve">L10 Lines</t>
+    <t xml:space="preserve">SA6 Lines</t>
   </si>
   <si>
     <t xml:space="preserve">Milne-Eddington LTE line profile and curve of growth</t>
@@ -616,7 +616,7 @@
     <t xml:space="preserve">An interactive web version with sliders (same physics) is in app/index.html of the course repository.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 1 - How much light gets through a slab of gas?</t>
+    <t xml:space="preserve">Lecture RT1 - How much light gets through a slab of gas?</t>
   </si>
   <si>
     <t xml:space="preserve">Absorption removes a fixed fraction of the beam per unit length. Optical depth counts mean free paths.</t>
@@ -667,7 +667,7 @@
     <t xml:space="preserve">I(s)/I(0)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 2 - Why a star looks equally bright per square arcsecond from any distance</t>
+    <t xml:space="preserve">Lecture RT2 - Why a star looks equally bright per square arcsecond from any distance</t>
   </si>
   <si>
     <t xml:space="preserve">Flux falls as 1/d^2, but the solid angle of the star falls in exactly the same way: their ratio, the intensity, is constant.</t>
@@ -745,7 +745,7 @@
     <t xml:space="preserve">I / I_surface</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 3 - How a black body changes with temperature</t>
+    <t xml:space="preserve">Lecture RT3 - How a black body changes with temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Raise T: the peak moves to shorter wavelengths (Wien) and the total flux grows as T^4 (Stefan-Boltzmann).</t>
@@ -799,7 +799,7 @@
     <t xml:space="preserve">Wien</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 4 - How long does light take to leave a star?</t>
+    <t xml:space="preserve">Lecture RT4 - How long does light take to leave a star?</t>
   </si>
   <si>
     <t xml:space="preserve">A scattered photon random-walks: after N steps of length l it is only sqrt(N) l away, so escaping from optical depth tau takes N ~ tau^2 steps.</t>
@@ -877,7 +877,7 @@
     <t xml:space="preserve">escape chance ~ exp(-tau sqrt(3 eps))</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 5 - Absorption or emission lines? A slab and the MIT 8.901 two-layer star</t>
+    <t xml:space="preserve">Lecture RT5 - Absorption or emission lines? A slab and the MIT 8.901 two-layer star</t>
   </si>
   <si>
     <t xml:space="preserve">The beam relaxes toward the source function. Lines are dark if the gas in front is cooler than the background, bright if hotter.</t>
@@ -970,7 +970,7 @@
     <t xml:space="preserve">B(T_top) [1e12]</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 6 - Why are Balmer lines strongest in A stars?</t>
+    <t xml:space="preserve">Lecture SA1 - Why are Balmer lines strongest in A stars?</t>
   </si>
   <si>
     <t xml:space="preserve">In LTE, excitation follows Boltzmann and ionisation follows Saha. The n=2 population (Balmer absorbers) peaks near 10 000 K.</t>
@@ -1018,7 +1018,7 @@
     <t xml:space="preserve">N2/N_total x 1e5</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 7 - What depth do we see at each point of the stellar disk?</t>
+    <t xml:space="preserve">Lecture RT7 - What depth do we see at each point of the stellar disk?</t>
   </si>
   <si>
     <t xml:space="preserve">The emergent intensity is S averaged with weight exp(-tau/mu)/mu. Eddington-Barbier: I(0,mu) ~ S(tau = mu), exact for linear S.</t>
@@ -1069,7 +1069,7 @@
     <t xml:space="preserve">weight exp(-tau/mu)/mu</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 8 - Why is S below B at the surface of an isothermal scattering atmosphere?</t>
+    <t xml:space="preserve">Lecture RT8 - Why is S below B at the surface of an isothermal scattering atmosphere?</t>
   </si>
   <si>
     <t xml:space="preserve">Photons scatter ~1/eps times before destruction and leak out within tau ~ 1/sqrt(eps) of the surface, so J and S fall below B there.</t>
@@ -1132,7 +1132,7 @@
     <t xml:space="preserve">Planck-type mean (arithmetic)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 9 - The complete gray LTE atmosphere</t>
+    <t xml:space="preserve">Lecture SA5 - The complete gray LTE atmosphere</t>
   </si>
   <si>
     <t xml:space="preserve">Exact solution (Hopf q, Chandrasekhar H) vs Eddington. The model scales with T_eff; limb darkening and spectrum are integrated numerically.</t>
@@ -1213,7 +1213,7 @@
     <t xml:space="preserve">pi B_lambda(T_eff)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture 10 - How does a spectral line grow? Milne-Eddington profiles and the curve of growth</t>
+    <t xml:space="preserve">Lecture SA6 - How does a spectral line grow? Milne-Eddington profiles and the curve of growth</t>
   </si>
   <si>
     <t xml:space="preserve">In LTE a line is dark because we see higher, cooler layers at its frequencies. Saturation: the core cannot drop below 1/(1+2beta/3).</t>
@@ -1959,7 +1959,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L1 Optical depth'!$E$17:$E$57</c:f>
+              <c:f>'RT1 Optical depth'!$E$17:$E$57</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="41"/>
@@ -2091,7 +2091,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L1 Optical depth'!$F$17:$F$57</c:f>
+              <c:f>'RT1 Optical depth'!$F$17:$F$57</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -2223,11 +2223,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="80872041"/>
-        <c:axId val="89889388"/>
+        <c:axId val="55305833"/>
+        <c:axId val="55375249"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="80872041"/>
+        <c:axId val="55305833"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2303,12 +2303,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89889388"/>
+        <c:crossAx val="55375249"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="89889388"/>
+        <c:axId val="55375249"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2386,7 +2386,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80872041"/>
+        <c:crossAx val="55305833"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2537,7 +2537,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L6 Saha-Boltzmann'!$E$18:$E$288</c:f>
+              <c:f>'SA1 Saha-Boltzmann'!$E$18:$E$288</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="271"/>
@@ -3359,7 +3359,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L6 Saha-Boltzmann'!$G$18:$G$288</c:f>
+              <c:f>'SA1 Saha-Boltzmann'!$G$18:$G$288</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="271"/>
@@ -4181,11 +4181,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="55824722"/>
-        <c:axId val="33457960"/>
+        <c:axId val="82484130"/>
+        <c:axId val="29187508"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="55824722"/>
+        <c:axId val="82484130"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4261,12 +4261,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33457960"/>
+        <c:crossAx val="29187508"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="33457960"/>
+        <c:axId val="29187508"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4343,7 +4343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55824722"/>
+        <c:crossAx val="82484130"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4494,7 +4494,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$E$20:$E$40</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$E$20:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4566,7 +4566,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$F$20:$F$40</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$F$20:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4638,11 +4638,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="41809109"/>
-        <c:axId val="6823353"/>
+        <c:axId val="49703797"/>
+        <c:axId val="16589848"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="41809109"/>
+        <c:axId val="49703797"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4720,12 +4720,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6823353"/>
+        <c:crossAx val="16589848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="6823353"/>
+        <c:axId val="16589848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4802,7 +4802,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41809109"/>
+        <c:crossAx val="49703797"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4953,7 +4953,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$H$20:$H$60</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$H$20:$H$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5085,7 +5085,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$I$20:$I$60</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$I$20:$I$60</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5217,11 +5217,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="86677402"/>
-        <c:axId val="18872482"/>
+        <c:axId val="62386877"/>
+        <c:axId val="21674412"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86677402"/>
+        <c:axId val="62386877"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5297,12 +5297,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18872482"/>
+        <c:crossAx val="21674412"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="18872482"/>
+        <c:axId val="21674412"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5378,7 +5378,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86677402"/>
+        <c:crossAx val="62386877"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5529,7 +5529,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$H$20:$H$60</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$H$20:$H$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5661,7 +5661,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L7 Eddington-Barbier'!$J$20:$J$60</c:f>
+              <c:f>'RT7 Eddington-Barbier'!$J$20:$J$60</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5793,11 +5793,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="62792385"/>
-        <c:axId val="85994011"/>
+        <c:axId val="23419116"/>
+        <c:axId val="80925745"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="62792385"/>
+        <c:axId val="23419116"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5873,12 +5873,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85994011"/>
+        <c:crossAx val="80925745"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="85994011"/>
+        <c:axId val="80925745"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +5954,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62792385"/>
+        <c:crossAx val="23419116"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6105,7 +6105,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L8 Scattering'!$E$17:$E$69</c:f>
+              <c:f>'RT8 Scattering'!$E$17:$E$69</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6273,7 +6273,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L8 Scattering'!$F$17:$F$69</c:f>
+              <c:f>'RT8 Scattering'!$F$17:$F$69</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6497,7 +6497,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L8 Scattering'!$E$17:$E$69</c:f>
+              <c:f>'RT8 Scattering'!$E$17:$E$69</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6665,7 +6665,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L8 Scattering'!$G$17:$G$69</c:f>
+              <c:f>'RT8 Scattering'!$G$17:$G$69</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6833,11 +6833,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="33324811"/>
-        <c:axId val="5739416"/>
+        <c:axId val="99705898"/>
+        <c:axId val="97062796"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="33324811"/>
+        <c:axId val="99705898"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -6914,12 +6914,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5739416"/>
+        <c:crossAx val="97062796"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="5739416"/>
+        <c:axId val="97062796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -6997,7 +6997,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33324811"/>
+        <c:crossAx val="99705898"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7148,7 +7148,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$E$32:$E$101</c:f>
+              <c:f>'SA5 Gray atmosphere'!$E$32:$E$101</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7367,7 +7367,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$I$32:$I$101</c:f>
+              <c:f>'SA5 Gray atmosphere'!$I$32:$I$101</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7642,7 +7642,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$E$32:$E$101</c:f>
+              <c:f>'SA5 Gray atmosphere'!$E$32:$E$101</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7861,7 +7861,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$J$32:$J$101</c:f>
+              <c:f>'SA5 Gray atmosphere'!$J$32:$J$101</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="70"/>
@@ -8080,11 +8080,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="67177614"/>
-        <c:axId val="26160713"/>
+        <c:axId val="75758088"/>
+        <c:axId val="85847200"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="67177614"/>
+        <c:axId val="75758088"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -8161,12 +8161,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26160713"/>
+        <c:crossAx val="85847200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="26160713"/>
+        <c:axId val="85847200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8242,7 +8242,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67177614"/>
+        <c:crossAx val="75758088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8393,7 +8393,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8465,7 +8465,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$O$20:$O$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$O$20:$O$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8593,7 +8593,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8665,7 +8665,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$P$20:$P$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$P$20:$P$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8793,7 +8793,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8865,7 +8865,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$Q$20:$Q$40</c:f>
+              <c:f>'SA5 Gray atmosphere'!$Q$20:$Q$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8937,11 +8937,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="29598448"/>
-        <c:axId val="23019515"/>
+        <c:axId val="46830083"/>
+        <c:axId val="69113022"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="29598448"/>
+        <c:axId val="46830083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9019,12 +9019,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23019515"/>
+        <c:crossAx val="69113022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="23019515"/>
+        <c:axId val="69113022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9102,7 +9102,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29598448"/>
+        <c:crossAx val="46830083"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9253,7 +9253,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$S$34:$S$144</c:f>
+              <c:f>'SA5 Gray atmosphere'!$S$34:$S$144</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="111"/>
@@ -9595,7 +9595,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$T$34:$T$144</c:f>
+              <c:f>'SA5 Gray atmosphere'!$T$34:$T$144</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="111"/>
@@ -9993,7 +9993,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$S$34:$S$144</c:f>
+              <c:f>'SA5 Gray atmosphere'!$S$34:$S$144</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="111"/>
@@ -10335,7 +10335,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L9 Gray atmosphere'!$V$34:$V$144</c:f>
+              <c:f>'SA5 Gray atmosphere'!$V$34:$V$144</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="111"/>
@@ -10677,11 +10677,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="26611103"/>
-        <c:axId val="20642649"/>
+        <c:axId val="34538824"/>
+        <c:axId val="47455286"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="26611103"/>
+        <c:axId val="34538824"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -10758,12 +10758,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20642649"/>
+        <c:crossAx val="47455286"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="20642649"/>
+        <c:axId val="47455286"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -10840,7 +10840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26611103"/>
+        <c:crossAx val="34538824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10991,7 +10991,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$E$26:$E$106</c:f>
+              <c:f>'SA6 Lines'!$E$26:$E$106</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="81"/>
@@ -11243,7 +11243,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$F$26:$F$106</c:f>
+              <c:f>'SA6 Lines'!$F$26:$F$106</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="81"/>
@@ -11495,11 +11495,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="49136741"/>
-        <c:axId val="24920184"/>
+        <c:axId val="29722737"/>
+        <c:axId val="81171067"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="49136741"/>
+        <c:axId val="29722737"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="8"/>
@@ -11577,12 +11577,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24920184"/>
+        <c:crossAx val="81171067"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="24920184"/>
+        <c:axId val="81171067"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11658,7 +11658,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49136741"/>
+        <c:crossAx val="29722737"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11809,7 +11809,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -11917,7 +11917,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$I$26:$I$58</c:f>
+              <c:f>'SA6 Lines'!$I$26:$I$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12081,7 +12081,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12189,7 +12189,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$J$26:$J$58</c:f>
+              <c:f>'SA6 Lines'!$J$26:$J$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12353,7 +12353,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12461,7 +12461,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L10 Lines'!$K$26:$K$58</c:f>
+              <c:f>'SA6 Lines'!$K$26:$K$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12569,11 +12569,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="42382133"/>
-        <c:axId val="39360737"/>
+        <c:axId val="89772214"/>
+        <c:axId val="11783439"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="42382133"/>
+        <c:axId val="89772214"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -12650,12 +12650,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39360737"/>
+        <c:crossAx val="11783439"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="39360737"/>
+        <c:axId val="11783439"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -12734,7 +12734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42382133"/>
+        <c:crossAx val="89772214"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -12885,7 +12885,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L2 Intensity'!$E$21:$E$53</c:f>
+              <c:f>'RT2 Intensity'!$E$21:$E$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12993,7 +12993,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L2 Intensity'!$F$21:$F$53</c:f>
+              <c:f>'RT2 Intensity'!$F$21:$F$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13157,7 +13157,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L2 Intensity'!$E$21:$E$53</c:f>
+              <c:f>'RT2 Intensity'!$E$21:$E$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13265,7 +13265,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L2 Intensity'!$H$21:$H$53</c:f>
+              <c:f>'RT2 Intensity'!$H$21:$H$53</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13373,11 +13373,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="53066553"/>
-        <c:axId val="98637902"/>
+        <c:axId val="77784081"/>
+        <c:axId val="10426368"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="53066553"/>
+        <c:axId val="77784081"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13454,12 +13454,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98637902"/>
+        <c:crossAx val="10426368"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="98637902"/>
+        <c:axId val="10426368"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13537,7 +13537,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53066553"/>
+        <c:crossAx val="77784081"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13688,7 +13688,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -13877,7 +13877,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$F$18:$F$77</c:f>
+              <c:f>'RT3 Planck'!$F$18:$F$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14122,7 +14122,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14311,7 +14311,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$G$18:$G$77</c:f>
+              <c:f>'RT3 Planck'!$G$18:$G$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14500,11 +14500,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="88050042"/>
-        <c:axId val="32382993"/>
+        <c:axId val="97253950"/>
+        <c:axId val="76239142"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="88050042"/>
+        <c:axId val="97253950"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="3000"/>
@@ -14582,12 +14582,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32382993"/>
+        <c:crossAx val="76239142"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="32382993"/>
+        <c:axId val="76239142"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14663,7 +14663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88050042"/>
+        <c:crossAx val="97253950"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -14814,7 +14814,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15003,7 +15003,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$F$18:$F$77</c:f>
+              <c:f>'RT3 Planck'!$F$18:$F$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15248,7 +15248,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15437,7 +15437,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$H$18:$H$77</c:f>
+              <c:f>'RT3 Planck'!$H$18:$H$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15682,7 +15682,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15871,7 +15871,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L3 Planck'!$I$18:$I$77</c:f>
+              <c:f>'RT3 Planck'!$I$18:$I$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -16060,11 +16060,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="66789461"/>
-        <c:axId val="59917220"/>
+        <c:axId val="77095345"/>
+        <c:axId val="18615844"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="66789461"/>
+        <c:axId val="77095345"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16141,12 +16141,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59917220"/>
+        <c:crossAx val="18615844"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="59917220"/>
+        <c:axId val="18615844"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16223,7 +16223,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66789461"/>
+        <c:crossAx val="77095345"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -16374,7 +16374,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L4 Random walk'!$E$23:$E$52</c:f>
+              <c:f>'RT4 Random walk'!$E$23:$E$52</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16473,7 +16473,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L4 Random walk'!$F$23:$F$52</c:f>
+              <c:f>'RT4 Random walk'!$F$23:$F$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16572,11 +16572,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="91926434"/>
-        <c:axId val="1332738"/>
+        <c:axId val="25006489"/>
+        <c:axId val="50078134"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="91926434"/>
+        <c:axId val="25006489"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16652,12 +16652,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1332738"/>
+        <c:crossAx val="50078134"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1332738"/>
+        <c:axId val="50078134"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16733,7 +16733,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91926434"/>
+        <c:crossAx val="25006489"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -16884,7 +16884,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L4 Random walk'!$E$23:$E$52</c:f>
+              <c:f>'RT4 Random walk'!$E$23:$E$52</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16983,7 +16983,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L4 Random walk'!$G$23:$G$52</c:f>
+              <c:f>'RT4 Random walk'!$G$23:$G$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="30"/>
@@ -17082,11 +17082,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="51004791"/>
-        <c:axId val="68309137"/>
+        <c:axId val="68042575"/>
+        <c:axId val="94061470"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="51004791"/>
+        <c:axId val="68042575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17162,12 +17162,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68309137"/>
+        <c:crossAx val="94061470"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="68309137"/>
+        <c:axId val="94061470"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -17245,7 +17245,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51004791"/>
+        <c:crossAx val="68042575"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -17396,7 +17396,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17498,7 +17498,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$F$26:$F$56</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$F$26:$F$56</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17656,7 +17656,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17758,7 +17758,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$G$26:$G$56</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$G$26:$G$56</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17860,11 +17860,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="61688933"/>
-        <c:axId val="50105011"/>
+        <c:axId val="40519366"/>
+        <c:axId val="73841220"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="61688933"/>
+        <c:axId val="40519366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17940,12 +17940,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50105011"/>
+        <c:crossAx val="73841220"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="50105011"/>
+        <c:axId val="73841220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -18022,7 +18022,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61688933"/>
+        <c:crossAx val="40519366"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -18173,7 +18173,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -19145,7 +19145,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$J$26:$J$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$J$26:$J$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -20173,7 +20173,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -21145,7 +21145,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$K$26:$K$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$K$26:$K$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -22173,7 +22173,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -23145,7 +23145,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L5 Slab &amp; MIT star'!$L$26:$L$346</c:f>
+              <c:f>'RT5 Slab &amp; MIT star'!$L$26:$L$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -24117,11 +24117,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="61955867"/>
-        <c:axId val="15597742"/>
+        <c:axId val="29653960"/>
+        <c:axId val="60706765"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="61955867"/>
+        <c:axId val="29653960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1000"/>
@@ -24199,12 +24199,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15597742"/>
+        <c:crossAx val="60706765"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="15597742"/>
+        <c:axId val="60706765"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -24280,7 +24280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61955867"/>
+        <c:crossAx val="29653960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -24431,7 +24431,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'L6 Saha-Boltzmann'!$E$18:$E$288</c:f>
+              <c:f>'SA1 Saha-Boltzmann'!$E$18:$E$288</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="271"/>
@@ -25253,7 +25253,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'L6 Saha-Boltzmann'!$F$18:$F$288</c:f>
+              <c:f>'SA1 Saha-Boltzmann'!$F$18:$F$288</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="271"/>
@@ -26075,11 +26075,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="87601805"/>
-        <c:axId val="78511801"/>
+        <c:axId val="4680732"/>
+        <c:axId val="98931320"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="87601805"/>
+        <c:axId val="4680732"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -26155,12 +26155,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78511801"/>
+        <c:crossAx val="98931320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="78511801"/>
+        <c:axId val="98931320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -26238,7 +26238,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87601805"/>
+        <c:crossAx val="4680732"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -27260,16 +27260,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A12" r:id="rId1" location="'L1%20Optical%20depth'!A1" display="L1 Optical depth"/>
-    <hyperlink ref="A13" r:id="rId2" location="'L2%20Intensity'!A1" display="L2 Intensity"/>
-    <hyperlink ref="A14" r:id="rId3" location="'L3%20Planck'!A1" display="L3 Planck"/>
-    <hyperlink ref="A15" r:id="rId4" location="'L4%20Random%20walk'!A1" display="L4 Random walk"/>
-    <hyperlink ref="A16" r:id="rId5" location="'L5%20Slab%20&amp;%20MIT%20star'!A1" display="L5 Slab &amp; MIT star"/>
-    <hyperlink ref="A17" r:id="rId6" location="'L6%20Saha-Boltzmann'!A1" display="L6 Saha-Boltzmann"/>
-    <hyperlink ref="A18" r:id="rId7" location="'L7%20Eddington-Barbier'!A1" display="L7 Eddington-Barbier"/>
-    <hyperlink ref="A19" r:id="rId8" location="'L8%20Scattering'!A1" display="L8 Scattering"/>
-    <hyperlink ref="A20" r:id="rId9" location="'L9%20Gray%20atmosphere'!A1" display="L9 Gray atmosphere"/>
-    <hyperlink ref="A21" r:id="rId10" location="'L10%20Lines'!A1" display="L10 Lines"/>
+    <hyperlink ref="A12" r:id="rId1" location="'RT1%20Optical%20depth'!A1" display="RT1 Optical depth"/>
+    <hyperlink ref="A13" r:id="rId2" location="'RT2%20Intensity'!A1" display="RT2 Intensity"/>
+    <hyperlink ref="A14" r:id="rId3" location="'RT3%20Planck'!A1" display="RT3 Planck"/>
+    <hyperlink ref="A15" r:id="rId4" location="'RT4%20Random%20walk'!A1" display="RT4 Random walk"/>
+    <hyperlink ref="A16" r:id="rId5" location="'RT5%20Slab%20&amp;%20MIT%20star'!A1" display="RT5 Slab &amp; MIT star"/>
+    <hyperlink ref="A17" r:id="rId6" location="'SA1%20Saha-Boltzmann'!A1" display="SA1 Saha-Boltzmann"/>
+    <hyperlink ref="A18" r:id="rId7" location="'RT7%20Eddington-Barbier'!A1" display="RT7 Eddington-Barbier"/>
+    <hyperlink ref="A19" r:id="rId8" location="'RT8%20Scattering'!A1" display="RT8 Scattering"/>
+    <hyperlink ref="A20" r:id="rId9" location="'SA5%20Gray%20atmosphere'!A1" display="SA5 Gray atmosphere"/>
+    <hyperlink ref="A21" r:id="rId10" location="'SA6%20Lines'!A1" display="SA6 Lines"/>
     <hyperlink ref="A22" r:id="rId11" location="'Constants'!A1" display="Constants"/>
     <hyperlink ref="A23" r:id="rId12" location="'Data'!A1" display="Data"/>
   </hyperlinks>

--- a/Radiative_Transfer_Lab.xlsx
+++ b/Radiative_Transfer_Lab.xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="RT1 Optical depth" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="RT2 Intensity" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RT3 Planck" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RT4 Random walk" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="RT5 Slab &amp; MIT star" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="RT1 Intensity" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="RT2 Planck" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RT2 Random walk" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RT3 Slab &amp; MIT star" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="SA1 Saha-Boltzmann" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="RT7 Eddington-Barbier" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="RT8 Scattering" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="SA5 Gray atmosphere" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="SA6 Lines" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="RT4 Eddington-Barbier" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="RT4 Scattering" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="SA4 Gray atmosphere" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="SA4 Lines" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Constants" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Data" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -65,6 +65,27 @@
           <t xml:space="preserve">Sun 5772 K. The gray solution is self-similar in T/T_eff.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -77,6 +98,27 @@
           <t xml:space="preserve">Compare 300 nm (strong darkening) with 1500 nm.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
@@ -89,6 +131,27 @@
           <t xml:space="preserve">Sun 4.44; giants ~2; white dwarfs ~8.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
@@ -101,13 +164,34 @@
           <t xml:space="preserve">Solar photosphere ~0.03 m^2/kg.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -123,6 +207,27 @@
           <t xml:space="preserve">B = B0 (1 + beta tau). beta = 0: isothermal, no line.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -135,6 +240,27 @@
           <t xml:space="preserve">Try 0.1 (weak), 10 (saturated), 1e5 (damping wings).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
@@ -147,6 +273,27 @@
           <t xml:space="preserve">Voigt damping. Set 0 for a pure Gaussian.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B10" authorId="0">
       <text>
@@ -159,13 +306,34 @@
           <t xml:space="preserve">Fe 55.8, Ca 40.1, Na 23.0, H 1.008</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -181,6 +349,27 @@
           <t xml:space="preserve">Fraction of the beam removed per km. Try 0.01 to 10.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -193,13 +382,34 @@
           <t xml:space="preserve">Total path through the gas. Try 0.1 to 20.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -215,6 +425,27 @@
           <t xml:space="preserve">Sun 5772 K; Sirius A 9940 K.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -227,6 +458,27 @@
           <t xml:space="preserve">Sun 1; Sirius A 1.711.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
@@ -239,13 +491,34 @@
           <t xml:space="preserve">Earth 1 AU, Mars 1.524 AU, Sirius 543900 AU.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -261,6 +534,27 @@
           <t xml:space="preserve">Try 3000 (red dwarf), 5772 (Sun), 10000 (A star), 30000 (O star).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -273,13 +567,34 @@
           <t xml:space="preserve">Second curve on the chart.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -295,6 +610,27 @@
           <t xml:space="preserve">Mass of the sphere in solar masses.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
@@ -307,6 +643,27 @@
           <t xml:space="preserve">Sets the electrons per unit mass: mu_e = 2/(1+X).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B9" authorId="0">
       <text>
@@ -319,13 +676,34 @@
           <t xml:space="preserve">Probability that an interaction destroys the photon (absorption).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -341,6 +719,27 @@
           <t xml:space="preserve">Brightness of the beam entering the slab, in units of S.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
@@ -353,6 +752,27 @@
           <t xml:space="preserve">Hot, optically thick base.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
@@ -365,6 +785,27 @@
           <t xml:space="preserve">Make it larger than T_base for a thermal inversion.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
@@ -377,6 +818,27 @@
           <t xml:space="preserve">Optical depth at the centre of H-alpha. Try 0.1 to 100.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
@@ -389,13 +851,34 @@
           <t xml:space="preserve">Use 0 for a thin cloud seen against empty sky.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -411,6 +894,27 @@
           <t xml:space="preserve">Try 5772 (Sun), 9900 (A0 star), 20000 (B star).</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -423,13 +927,34 @@
           <t xml:space="preserve">Typical photospheres: 1 to 100 Pa.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -445,6 +970,27 @@
           <t xml:space="preserve">Solar 500 nm: a = 0.36 with b = 0.64.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B7" authorId="0">
       <text>
@@ -457,6 +1003,27 @@
           <t xml:space="preserve">b &gt; 0: S increases inward -&gt; limb darkening. b &lt; 0: limb brightening.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B8" authorId="0">
       <text>
@@ -469,13 +1036,34 @@
           <t xml:space="preserve">c = 0 makes Eddington-Barbier exact.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -491,6 +1079,27 @@
           <t xml:space="preserve">1 = pure absorption (LTE). Try 0.1, 0.01, 0.001.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>-58</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
@@ -502,7 +1111,7 @@
     <t xml:space="preserve">Radiative Transfer Lab (spreadsheet edition)</t>
   </si>
   <si>
-    <t xml:space="preserve">Companion to the course 'Radiative Transfer: a graduated course for pre-master students'. One sheet per lecture.</t>
+    <t xml:space="preserve">Companion to the two courses 'Radiative Transfer' (RT1-RT6) and 'Stellar Atmospheres' (SA1-SA5). One sheet per experiment, labelled with its lecture.</t>
   </si>
   <si>
     <t xml:space="preserve">How to use</t>
@@ -547,25 +1156,25 @@
     <t xml:space="preserve">Beam attenuation, optical depth, magnitudes of extinction</t>
   </si>
   <si>
-    <t xml:space="preserve">RT2 Intensity</t>
+    <t xml:space="preserve">RT1 Intensity</t>
   </si>
   <si>
     <t xml:space="preserve">Flux falls as 1/d^2, solid angle too: intensity is conserved</t>
   </si>
   <si>
-    <t xml:space="preserve">RT3 Planck</t>
+    <t xml:space="preserve">RT2 Planck</t>
   </si>
   <si>
     <t xml:space="preserve">Black-body spectrum, Wien peak, Stefan-Boltzmann, RJ and Wien limits</t>
   </si>
   <si>
-    <t xml:space="preserve">RT4 Random walk</t>
+    <t xml:space="preserve">RT2 Random walk</t>
   </si>
   <si>
     <t xml:space="preserve">Mean free path, photon diffusion time, thermalisation depth</t>
   </si>
   <si>
-    <t xml:space="preserve">RT5 Slab &amp; MIT star</t>
+    <t xml:space="preserve">RT3 Slab &amp; MIT star</t>
   </si>
   <si>
     <t xml:space="preserve">Slab solution; MIT two-layer star with Balmer + Paschen lines; thermal inversion</t>
@@ -577,25 +1186,25 @@
     <t xml:space="preserve">Hydrogen ionisation and n=2 population; why Balmer lines peak in A stars</t>
   </si>
   <si>
-    <t xml:space="preserve">RT7 Eddington-Barbier</t>
+    <t xml:space="preserve">RT4 Eddington-Barbier</t>
   </si>
   <si>
     <t xml:space="preserve">Emergent intensity, limb darkening, Eddington-Barbier error</t>
   </si>
   <si>
-    <t xml:space="preserve">RT8 Scattering</t>
+    <t xml:space="preserve">RT4 Scattering</t>
   </si>
   <si>
     <t xml:space="preserve">S = eps B + (1-eps) J: Eddington solution, sqrt(eps) law; Rosseland mean calculator</t>
   </si>
   <si>
-    <t xml:space="preserve">SA5 Gray atmosphere</t>
+    <t xml:space="preserve">SA4 Gray atmosphere</t>
   </si>
   <si>
     <t xml:space="preserve">Exact gray LTE model: T(tau), limb darkening at any wavelength, emergent spectrum, pressure</t>
   </si>
   <si>
-    <t xml:space="preserve">SA6 Lines</t>
+    <t xml:space="preserve">SA4 Lines</t>
   </si>
   <si>
     <t xml:space="preserve">Milne-Eddington LTE line profile and curve of growth</t>
@@ -667,7 +1276,7 @@
     <t xml:space="preserve">I(s)/I(0)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT2 - Why a star looks equally bright per square arcsecond from any distance</t>
+    <t xml:space="preserve">Lecture RT1 - Why a star looks equally bright per square arcsecond from any distance</t>
   </si>
   <si>
     <t xml:space="preserve">Flux falls as 1/d^2, but the solid angle of the star falls in exactly the same way: their ratio, the intensity, is constant.</t>
@@ -745,7 +1354,7 @@
     <t xml:space="preserve">I / I_surface</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT3 - How a black body changes with temperature</t>
+    <t xml:space="preserve">Lecture RT2 - How a black body changes with temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Raise T: the peak moves to shorter wavelengths (Wien) and the total flux grows as T^4 (Stefan-Boltzmann).</t>
@@ -799,7 +1408,7 @@
     <t xml:space="preserve">Wien</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT4 - How long does light take to leave a star?</t>
+    <t xml:space="preserve">Lecture RT2 - How long does light take to leave a star?</t>
   </si>
   <si>
     <t xml:space="preserve">A scattered photon random-walks: after N steps of length l it is only sqrt(N) l away, so escaping from optical depth tau takes N ~ tau^2 steps.</t>
@@ -877,7 +1486,7 @@
     <t xml:space="preserve">escape chance ~ exp(-tau sqrt(3 eps))</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT5 - Absorption or emission lines? A slab and the MIT 8.901 two-layer star</t>
+    <t xml:space="preserve">Lecture RT3 - Absorption or emission lines? A slab and the MIT 8.901 two-layer star</t>
   </si>
   <si>
     <t xml:space="preserve">The beam relaxes toward the source function. Lines are dark if the gas in front is cooler than the background, bright if hotter.</t>
@@ -1018,7 +1627,7 @@
     <t xml:space="preserve">N2/N_total x 1e5</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT7 - What depth do we see at each point of the stellar disk?</t>
+    <t xml:space="preserve">Lecture RT4 - What depth do we see at each point of the stellar disk?</t>
   </si>
   <si>
     <t xml:space="preserve">The emergent intensity is S averaged with weight exp(-tau/mu)/mu. Eddington-Barbier: I(0,mu) ~ S(tau = mu), exact for linear S.</t>
@@ -1069,7 +1678,7 @@
     <t xml:space="preserve">weight exp(-tau/mu)/mu</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture RT8 - Why is S below B at the surface of an isothermal scattering atmosphere?</t>
+    <t xml:space="preserve">Lecture RT4 - Why is S below B at the surface of an isothermal scattering atmosphere?</t>
   </si>
   <si>
     <t xml:space="preserve">Photons scatter ~1/eps times before destruction and leak out within tau ~ 1/sqrt(eps) of the surface, so J and S fall below B there.</t>
@@ -1132,7 +1741,7 @@
     <t xml:space="preserve">Planck-type mean (arithmetic)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture SA5 - The complete gray LTE atmosphere</t>
+    <t xml:space="preserve">Lecture SA4 - The complete gray LTE atmosphere</t>
   </si>
   <si>
     <t xml:space="preserve">Exact solution (Hopf q, Chandrasekhar H) vs Eddington. The model scales with T_eff; limb darkening and spectrum are integrated numerically.</t>
@@ -1213,7 +1822,7 @@
     <t xml:space="preserve">pi B_lambda(T_eff)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture SA6 - How does a spectral line grow? Milne-Eddington profiles and the curve of growth</t>
+    <t xml:space="preserve">Lecture SA4 - How does a spectral line grow? Milne-Eddington profiles and the curve of growth</t>
   </si>
   <si>
     <t xml:space="preserve">In LTE a line is dark because we see higher, cooler layers at its frequencies. Saturation: the core cannot drop below 1/(1+2beta/3).</t>
@@ -2223,11 +2832,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="55305833"/>
-        <c:axId val="55375249"/>
+        <c:axId val="32607907"/>
+        <c:axId val="4105414"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="55305833"/>
+        <c:axId val="32607907"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2303,12 +2912,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55375249"/>
+        <c:crossAx val="4105414"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="55375249"/>
+        <c:axId val="4105414"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2386,7 +2995,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55305833"/>
+        <c:crossAx val="32607907"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4181,11 +4790,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="82484130"/>
-        <c:axId val="29187508"/>
+        <c:axId val="94098732"/>
+        <c:axId val="25155581"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="82484130"/>
+        <c:axId val="94098732"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4261,12 +4870,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29187508"/>
+        <c:crossAx val="25155581"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="29187508"/>
+        <c:axId val="25155581"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4343,7 +4952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82484130"/>
+        <c:crossAx val="94098732"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4494,7 +5103,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$E$20:$E$40</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$E$20:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4566,7 +5175,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$F$20:$F$40</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$F$20:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -4638,11 +5247,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="49703797"/>
-        <c:axId val="16589848"/>
+        <c:axId val="26976167"/>
+        <c:axId val="7416438"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="49703797"/>
+        <c:axId val="26976167"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4720,12 +5329,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16589848"/>
+        <c:crossAx val="7416438"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="16589848"/>
+        <c:axId val="7416438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4802,7 +5411,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49703797"/>
+        <c:crossAx val="26976167"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4953,7 +5562,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$H$20:$H$60</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$H$20:$H$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5085,7 +5694,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$I$20:$I$60</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$I$20:$I$60</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5217,11 +5826,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="62386877"/>
-        <c:axId val="21674412"/>
+        <c:axId val="10219871"/>
+        <c:axId val="1885089"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="62386877"/>
+        <c:axId val="10219871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5297,12 +5906,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21674412"/>
+        <c:crossAx val="1885089"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="21674412"/>
+        <c:axId val="1885089"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5378,7 +5987,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62386877"/>
+        <c:crossAx val="10219871"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5529,7 +6138,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$H$20:$H$60</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$H$20:$H$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5661,7 +6270,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT7 Eddington-Barbier'!$J$20:$J$60</c:f>
+              <c:f>'RT4 Eddington-Barbier'!$J$20:$J$60</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5793,11 +6402,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="23419116"/>
-        <c:axId val="80925745"/>
+        <c:axId val="17045295"/>
+        <c:axId val="57552872"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="23419116"/>
+        <c:axId val="17045295"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5873,12 +6482,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80925745"/>
+        <c:crossAx val="57552872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="80925745"/>
+        <c:axId val="57552872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5954,7 +6563,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23419116"/>
+        <c:crossAx val="17045295"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6105,7 +6714,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT8 Scattering'!$E$17:$E$69</c:f>
+              <c:f>'RT4 Scattering'!$E$17:$E$69</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6273,7 +6882,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT8 Scattering'!$F$17:$F$69</c:f>
+              <c:f>'RT4 Scattering'!$F$17:$F$69</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6497,7 +7106,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT8 Scattering'!$E$17:$E$69</c:f>
+              <c:f>'RT4 Scattering'!$E$17:$E$69</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6665,7 +7274,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT8 Scattering'!$G$17:$G$69</c:f>
+              <c:f>'RT4 Scattering'!$G$17:$G$69</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="53"/>
@@ -6833,11 +7442,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="99705898"/>
-        <c:axId val="97062796"/>
+        <c:axId val="57148572"/>
+        <c:axId val="83867156"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="99705898"/>
+        <c:axId val="57148572"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -6914,12 +7523,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97062796"/>
+        <c:crossAx val="83867156"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="97062796"/>
+        <c:axId val="83867156"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -6997,7 +7606,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99705898"/>
+        <c:crossAx val="57148572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7148,7 +7757,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$E$32:$E$101</c:f>
+              <c:f>'SA4 Gray atmosphere'!$E$32:$E$101</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7367,7 +7976,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$I$32:$I$101</c:f>
+              <c:f>'SA4 Gray atmosphere'!$I$32:$I$101</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7642,7 +8251,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$E$32:$E$101</c:f>
+              <c:f>'SA4 Gray atmosphere'!$E$32:$E$101</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="70"/>
@@ -7861,7 +8470,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$J$32:$J$101</c:f>
+              <c:f>'SA4 Gray atmosphere'!$J$32:$J$101</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="70"/>
@@ -8080,11 +8689,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="75758088"/>
-        <c:axId val="85847200"/>
+        <c:axId val="87500168"/>
+        <c:axId val="40134461"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="75758088"/>
+        <c:axId val="87500168"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -8161,12 +8770,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85847200"/>
+        <c:crossAx val="40134461"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="85847200"/>
+        <c:axId val="40134461"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8242,7 +8851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75758088"/>
+        <c:crossAx val="87500168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8393,7 +9002,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8465,7 +9074,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$O$20:$O$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$O$20:$O$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8593,7 +9202,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8665,7 +9274,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$P$20:$P$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$P$20:$P$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8793,7 +9402,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$M$20:$M$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$M$20:$M$40</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8865,7 +9474,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$Q$20:$Q$40</c:f>
+              <c:f>'SA4 Gray atmosphere'!$Q$20:$Q$40</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
@@ -8937,11 +9546,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="46830083"/>
-        <c:axId val="69113022"/>
+        <c:axId val="83647709"/>
+        <c:axId val="14761341"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="46830083"/>
+        <c:axId val="83647709"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9019,12 +9628,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69113022"/>
+        <c:crossAx val="14761341"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="69113022"/>
+        <c:axId val="14761341"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9102,7 +9711,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46830083"/>
+        <c:crossAx val="83647709"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9253,7 +9862,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$S$34:$S$144</c:f>
+              <c:f>'SA4 Gray atmosphere'!$S$34:$S$144</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="111"/>
@@ -9595,7 +10204,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$T$34:$T$144</c:f>
+              <c:f>'SA4 Gray atmosphere'!$T$34:$T$144</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="111"/>
@@ -9993,7 +10602,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$S$34:$S$144</c:f>
+              <c:f>'SA4 Gray atmosphere'!$S$34:$S$144</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="111"/>
@@ -10335,7 +10944,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA5 Gray atmosphere'!$V$34:$V$144</c:f>
+              <c:f>'SA4 Gray atmosphere'!$V$34:$V$144</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="111"/>
@@ -10677,11 +11286,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="34538824"/>
-        <c:axId val="47455286"/>
+        <c:axId val="56528756"/>
+        <c:axId val="28913528"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="34538824"/>
+        <c:axId val="56528756"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -10758,12 +11367,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47455286"/>
+        <c:crossAx val="28913528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="47455286"/>
+        <c:axId val="28913528"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -10840,7 +11449,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34538824"/>
+        <c:crossAx val="56528756"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10991,7 +11600,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$E$26:$E$106</c:f>
+              <c:f>'SA4 Lines'!$E$26:$E$106</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="81"/>
@@ -11243,7 +11852,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$F$26:$F$106</c:f>
+              <c:f>'SA4 Lines'!$F$26:$F$106</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="81"/>
@@ -11495,11 +12104,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="29722737"/>
-        <c:axId val="81171067"/>
+        <c:axId val="46651933"/>
+        <c:axId val="76463050"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="29722737"/>
+        <c:axId val="46651933"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="8"/>
@@ -11577,12 +12186,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81171067"/>
+        <c:crossAx val="76463050"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="81171067"/>
+        <c:axId val="76463050"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11658,7 +12267,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29722737"/>
+        <c:crossAx val="46651933"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -11809,7 +12418,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA4 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -11917,7 +12526,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$I$26:$I$58</c:f>
+              <c:f>'SA4 Lines'!$I$26:$I$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12081,7 +12690,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA4 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12189,7 +12798,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$J$26:$J$58</c:f>
+              <c:f>'SA4 Lines'!$J$26:$J$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12353,7 +12962,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$H$26:$H$58</c:f>
+              <c:f>'SA4 Lines'!$H$26:$H$58</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12461,7 +13070,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'SA6 Lines'!$K$26:$K$58</c:f>
+              <c:f>'SA4 Lines'!$K$26:$K$58</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12569,11 +13178,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="89772214"/>
-        <c:axId val="11783439"/>
+        <c:axId val="51640941"/>
+        <c:axId val="37481122"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="89772214"/>
+        <c:axId val="51640941"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -12650,12 +13259,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11783439"/>
+        <c:crossAx val="37481122"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="11783439"/>
+        <c:axId val="37481122"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -12734,7 +13343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89772214"/>
+        <c:crossAx val="51640941"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -12885,7 +13494,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT2 Intensity'!$E$21:$E$53</c:f>
+              <c:f>'RT1 Intensity'!$E$21:$E$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -12993,7 +13602,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT2 Intensity'!$F$21:$F$53</c:f>
+              <c:f>'RT1 Intensity'!$F$21:$F$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13157,7 +13766,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT2 Intensity'!$E$21:$E$53</c:f>
+              <c:f>'RT1 Intensity'!$E$21:$E$53</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13265,7 +13874,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT2 Intensity'!$H$21:$H$53</c:f>
+              <c:f>'RT1 Intensity'!$H$21:$H$53</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="33"/>
@@ -13373,11 +13982,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="77784081"/>
-        <c:axId val="10426368"/>
+        <c:axId val="60181612"/>
+        <c:axId val="17782534"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="77784081"/>
+        <c:axId val="60181612"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13454,12 +14063,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10426368"/>
+        <c:crossAx val="17782534"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="10426368"/>
+        <c:axId val="17782534"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13537,7 +14146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77784081"/>
+        <c:crossAx val="60181612"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13688,7 +14297,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT2 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -13877,7 +14486,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$F$18:$F$77</c:f>
+              <c:f>'RT2 Planck'!$F$18:$F$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14122,7 +14731,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT2 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14311,7 +14920,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$G$18:$G$77</c:f>
+              <c:f>'RT2 Planck'!$G$18:$G$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -14500,11 +15109,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="97253950"/>
-        <c:axId val="76239142"/>
+        <c:axId val="8374578"/>
+        <c:axId val="44542293"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="97253950"/>
+        <c:axId val="8374578"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="3000"/>
@@ -14582,12 +15191,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76239142"/>
+        <c:crossAx val="44542293"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76239142"/>
+        <c:axId val="44542293"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14663,7 +15272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97253950"/>
+        <c:crossAx val="8374578"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -14814,7 +15423,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT2 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15003,7 +15612,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$F$18:$F$77</c:f>
+              <c:f>'RT2 Planck'!$F$18:$F$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15248,7 +15857,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT2 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15437,7 +16046,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$H$18:$H$77</c:f>
+              <c:f>'RT2 Planck'!$H$18:$H$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15682,7 +16291,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$E$18:$E$77</c:f>
+              <c:f>'RT2 Planck'!$E$18:$E$77</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="60"/>
@@ -15871,7 +16480,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT3 Planck'!$I$18:$I$77</c:f>
+              <c:f>'RT2 Planck'!$I$18:$I$77</c:f>
               <c:numCache>
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="60"/>
@@ -16060,11 +16669,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="77095345"/>
-        <c:axId val="18615844"/>
+        <c:axId val="87443349"/>
+        <c:axId val="36178552"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="77095345"/>
+        <c:axId val="87443349"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16141,12 +16750,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18615844"/>
+        <c:crossAx val="36178552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="18615844"/>
+        <c:axId val="36178552"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16223,7 +16832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77095345"/>
+        <c:crossAx val="87443349"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -16374,7 +16983,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT4 Random walk'!$E$23:$E$52</c:f>
+              <c:f>'RT2 Random walk'!$E$23:$E$52</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16473,7 +17082,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT4 Random walk'!$F$23:$F$52</c:f>
+              <c:f>'RT2 Random walk'!$F$23:$F$52</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16572,11 +17181,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="25006489"/>
-        <c:axId val="50078134"/>
+        <c:axId val="97346656"/>
+        <c:axId val="38452845"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="25006489"/>
+        <c:axId val="97346656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16652,12 +17261,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50078134"/>
+        <c:crossAx val="38452845"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="50078134"/>
+        <c:axId val="38452845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16733,7 +17342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25006489"/>
+        <c:crossAx val="97346656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -16884,7 +17493,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT4 Random walk'!$E$23:$E$52</c:f>
+              <c:f>'RT2 Random walk'!$E$23:$E$52</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -16983,7 +17592,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT4 Random walk'!$G$23:$G$52</c:f>
+              <c:f>'RT2 Random walk'!$G$23:$G$52</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="30"/>
@@ -17082,11 +17691,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="68042575"/>
-        <c:axId val="94061470"/>
+        <c:axId val="32177355"/>
+        <c:axId val="60273095"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="68042575"/>
+        <c:axId val="32177355"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17162,12 +17771,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94061470"/>
+        <c:crossAx val="60273095"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="94061470"/>
+        <c:axId val="60273095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -17245,7 +17854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68042575"/>
+        <c:crossAx val="32177355"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -17396,7 +18005,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$E$26:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17498,7 +18107,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$F$26:$F$56</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$F$26:$F$56</c:f>
               <c:numCache>
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17656,7 +18265,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$E$26:$E$56</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$E$26:$E$56</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17758,7 +18367,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$G$26:$G$56</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$G$26:$G$56</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="31"/>
@@ -17860,11 +18469,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="40519366"/>
-        <c:axId val="73841220"/>
+        <c:axId val="63769224"/>
+        <c:axId val="75388820"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="40519366"/>
+        <c:axId val="63769224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17940,12 +18549,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73841220"/>
+        <c:crossAx val="75388820"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="73841220"/>
+        <c:axId val="75388820"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -18022,7 +18631,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40519366"/>
+        <c:crossAx val="63769224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -18173,7 +18782,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -19145,7 +19754,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$J$26:$J$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$J$26:$J$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -20173,7 +20782,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -21145,7 +21754,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$K$26:$K$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$K$26:$K$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -22173,7 +22782,7 @@
           </c:dLbls>
           <c:xVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$H$26:$H$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$H$26:$H$346</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="321"/>
@@ -23145,7 +23754,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'RT5 Slab &amp; MIT star'!$L$26:$L$346</c:f>
+              <c:f>'RT3 Slab &amp; MIT star'!$L$26:$L$346</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="321"/>
@@ -24117,11 +24726,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="29653960"/>
-        <c:axId val="60706765"/>
+        <c:axId val="19191217"/>
+        <c:axId val="16478523"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="29653960"/>
+        <c:axId val="19191217"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1000"/>
@@ -24199,12 +24808,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60706765"/>
+        <c:crossAx val="16478523"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="60706765"/>
+        <c:axId val="16478523"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -24280,7 +24889,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29653960"/>
+        <c:crossAx val="19191217"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -26075,11 +26684,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="4680732"/>
-        <c:axId val="98931320"/>
+        <c:axId val="5788534"/>
+        <c:axId val="31707399"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="4680732"/>
+        <c:axId val="5788534"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -26155,12 +26764,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98931320"/>
+        <c:crossAx val="31707399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="98931320"/>
+        <c:axId val="31707399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -26238,7 +26847,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4680732"/>
+        <c:crossAx val="5788534"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -27261,15 +27870,15 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A12" r:id="rId1" location="'RT1%20Optical%20depth'!A1" display="RT1 Optical depth"/>
-    <hyperlink ref="A13" r:id="rId2" location="'RT2%20Intensity'!A1" display="RT2 Intensity"/>
-    <hyperlink ref="A14" r:id="rId3" location="'RT3%20Planck'!A1" display="RT3 Planck"/>
-    <hyperlink ref="A15" r:id="rId4" location="'RT4%20Random%20walk'!A1" display="RT4 Random walk"/>
-    <hyperlink ref="A16" r:id="rId5" location="'RT5%20Slab%20&amp;%20MIT%20star'!A1" display="RT5 Slab &amp; MIT star"/>
+    <hyperlink ref="A13" r:id="rId2" location="'RT1%20Intensity'!A1" display="RT1 Intensity"/>
+    <hyperlink ref="A14" r:id="rId3" location="'RT2%20Planck'!A1" display="RT2 Planck"/>
+    <hyperlink ref="A15" r:id="rId4" location="'RT2%20Random%20walk'!A1" display="RT2 Random walk"/>
+    <hyperlink ref="A16" r:id="rId5" location="'RT3%20Slab%20&amp;%20MIT%20star'!A1" display="RT3 Slab &amp; MIT star"/>
     <hyperlink ref="A17" r:id="rId6" location="'SA1%20Saha-Boltzmann'!A1" display="SA1 Saha-Boltzmann"/>
-    <hyperlink ref="A18" r:id="rId7" location="'RT7%20Eddington-Barbier'!A1" display="RT7 Eddington-Barbier"/>
-    <hyperlink ref="A19" r:id="rId8" location="'RT8%20Scattering'!A1" display="RT8 Scattering"/>
-    <hyperlink ref="A20" r:id="rId9" location="'SA5%20Gray%20atmosphere'!A1" display="SA5 Gray atmosphere"/>
-    <hyperlink ref="A21" r:id="rId10" location="'SA6%20Lines'!A1" display="SA6 Lines"/>
+    <hyperlink ref="A18" r:id="rId7" location="'RT4%20Eddington-Barbier'!A1" display="RT4 Eddington-Barbier"/>
+    <hyperlink ref="A19" r:id="rId8" location="'RT4%20Scattering'!A1" display="RT4 Scattering"/>
+    <hyperlink ref="A20" r:id="rId9" location="'SA4%20Gray%20atmosphere'!A1" display="SA4 Gray atmosphere"/>
+    <hyperlink ref="A21" r:id="rId10" location="'SA4%20Lines'!A1" display="SA4 Lines"/>
     <hyperlink ref="A22" r:id="rId11" location="'Constants'!A1" display="Constants"/>
     <hyperlink ref="A23" r:id="rId12" location="'Data'!A1" display="Data"/>
   </hyperlinks>

--- a/Radiative_Transfer_Lab.xlsx
+++ b/Radiative_Transfer_Lab.xlsx
@@ -2832,11 +2832,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="32607907"/>
-        <c:axId val="4105414"/>
+        <c:axId val="95336551"/>
+        <c:axId val="67231371"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32607907"/>
+        <c:axId val="95336551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2912,12 +2912,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4105414"/>
+        <c:crossAx val="67231371"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="4105414"/>
+        <c:axId val="67231371"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2995,7 +2995,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32607907"/>
+        <c:crossAx val="95336551"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4790,11 +4790,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="94098732"/>
-        <c:axId val="25155581"/>
+        <c:axId val="13895401"/>
+        <c:axId val="31297303"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="94098732"/>
+        <c:axId val="13895401"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4870,12 +4870,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25155581"/>
+        <c:crossAx val="31297303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="25155581"/>
+        <c:axId val="31297303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -4952,7 +4952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94098732"/>
+        <c:crossAx val="13895401"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5247,11 +5247,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="26976167"/>
-        <c:axId val="7416438"/>
+        <c:axId val="34532996"/>
+        <c:axId val="62015311"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="26976167"/>
+        <c:axId val="34532996"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -5329,12 +5329,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7416438"/>
+        <c:crossAx val="62015311"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="7416438"/>
+        <c:axId val="62015311"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -5411,7 +5411,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26976167"/>
+        <c:crossAx val="34532996"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5826,11 +5826,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="10219871"/>
-        <c:axId val="1885089"/>
+        <c:axId val="52352366"/>
+        <c:axId val="15039033"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="10219871"/>
+        <c:axId val="52352366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5906,12 +5906,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1885089"/>
+        <c:crossAx val="15039033"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1885089"/>
+        <c:axId val="15039033"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5987,7 +5987,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10219871"/>
+        <c:crossAx val="52352366"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6402,11 +6402,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="17045295"/>
-        <c:axId val="57552872"/>
+        <c:axId val="42508578"/>
+        <c:axId val="79381008"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="17045295"/>
+        <c:axId val="42508578"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6482,12 +6482,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57552872"/>
+        <c:crossAx val="79381008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="57552872"/>
+        <c:axId val="79381008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6563,7 +6563,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17045295"/>
+        <c:crossAx val="42508578"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7442,11 +7442,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="57148572"/>
-        <c:axId val="83867156"/>
+        <c:axId val="96909985"/>
+        <c:axId val="76767503"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="57148572"/>
+        <c:axId val="96909985"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -7523,12 +7523,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83867156"/>
+        <c:crossAx val="76767503"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="83867156"/>
+        <c:axId val="76767503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -7606,7 +7606,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57148572"/>
+        <c:crossAx val="96909985"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7981,193 +7981,193 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="70"/>
                 <c:pt idx="0">
-                  <c:v>4687.69102634296</c:v>
+                  <c:v>4687.69102634295</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4688.48134699371</c:v>
+                  <c:v>4688.4813469937</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4689.38255750344</c:v>
+                  <c:v>4689.38255750343</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4690.40986124708</c:v>
+                  <c:v>4690.40986124706</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4691.58047834856</c:v>
+                  <c:v>4691.58047834855</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4692.91389989854</c:v>
+                  <c:v>4692.91389989852</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4694.43217149548</c:v>
+                  <c:v>4694.43217149547</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4696.16020890835</c:v>
+                  <c:v>4696.16020890834</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4698.12614879112</c:v>
+                  <c:v>4698.1261487911</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4700.36173748223</c:v>
+                  <c:v>4700.36173748222</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4702.90276098299</c:v>
+                  <c:v>4702.90276098297</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4705.78926039965</c:v>
+                  <c:v>4705.78926039964</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4709.06652742572</c:v>
+                  <c:v>4709.0665274257</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4712.78564684139</c:v>
+                  <c:v>4712.78564684137</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4717.00376002962</c:v>
+                  <c:v>4717.0037600296</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4721.78491423875</c:v>
+                  <c:v>4721.78491423873</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4727.20079794397</c:v>
+                  <c:v>4727.20079794396</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4733.331533474</c:v>
+                  <c:v>4733.33153347399</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4740.26652664715</c:v>
+                  <c:v>4740.26652664714</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4748.10537185658</c:v>
+                  <c:v>4748.10537185657</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4756.95880944098</c:v>
+                  <c:v>4756.95880944096</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4766.94973025255</c:v>
+                  <c:v>4766.94973025254</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4778.21422007525</c:v>
+                  <c:v>4778.21422007524</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4790.9026339536</c:v>
+                  <c:v>4790.90263395359</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4805.18068758967</c:v>
+                  <c:v>4805.18068758965</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4821.23054979749</c:v>
+                  <c:v>4821.23054979748</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4839.24898166427</c:v>
+                  <c:v>4839.24898166426</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4859.45624949731</c:v>
+                  <c:v>4859.4562494973</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4882.09026824236</c:v>
+                  <c:v>4882.09026824235</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4907.40914964674</c:v>
+                  <c:v>4907.40914964673</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4935.69215633088</c:v>
+                  <c:v>4935.69215633087</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4967.24028701626</c:v>
+                  <c:v>4967.24028701624</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5002.37666485136</c:v>
+                  <c:v>5002.37666485134</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>5041.44669287679</c:v>
+                  <c:v>5041.44669287678</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>5084.81794107236</c:v>
+                  <c:v>5084.81794107234</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5132.87973068102</c:v>
+                  <c:v>5132.87973068101</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5186.04238344752</c:v>
+                  <c:v>5186.04238344751</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5244.73610581189</c:v>
+                  <c:v>5244.73610581188</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5309.40948073326</c:v>
+                  <c:v>5309.40948073325</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5380.52754258322</c:v>
+                  <c:v>5380.52754258321</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5458.5670961725</c:v>
+                  <c:v>5458.56709617249</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5544.01507401578</c:v>
+                  <c:v>5544.01507401576</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>5637.37597814017</c:v>
+                  <c:v>5637.37597814016</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>5739.15278555111</c:v>
+                  <c:v>5739.15278555109</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>5849.84849637938</c:v>
+                  <c:v>5849.84849637937</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>5969.96149680783</c:v>
+                  <c:v>5969.96149680781</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>6099.98060610439</c:v>
+                  <c:v>6099.98060610437</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>6240.37995888259</c:v>
+                  <c:v>6240.37995888257</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>6391.61394662092</c:v>
+                  <c:v>6391.6139466209</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>6554.11252291001</c:v>
+                  <c:v>6554.11252290999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>6728.27725235617</c:v>
+                  <c:v>6728.27725235615</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>6914.47853431871</c:v>
+                  <c:v>6914.47853431869</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>7113.05443536212</c:v>
+                  <c:v>7113.0544353621</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>7324.31149390556</c:v>
+                  <c:v>7324.31149390554</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>7548.52770096623</c:v>
+                  <c:v>7548.52770096621</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>7785.95734347338</c:v>
+                  <c:v>7785.95734347336</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>8036.83889292048</c:v>
+                  <c:v>8036.83889292046</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>8301.40198687696</c:v>
+                  <c:v>8301.40198687694</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>8579.87612203612</c:v>
+                  <c:v>8579.8761220361</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>8872.49890159568</c:v>
+                  <c:v>8872.49890159566</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>9179.52291123178</c:v>
+                  <c:v>9179.52291123175</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>9501.22114553663</c:v>
+                  <c:v>9501.2211455366</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>9837.89098449824</c:v>
+                  <c:v>9837.89098449822</c:v>
                 </c:pt>
                 <c:pt idx="63">
                   <c:v>10189.8569554609</c:v>
@@ -8689,11 +8689,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="87500168"/>
-        <c:axId val="40134461"/>
+        <c:axId val="92660372"/>
+        <c:axId val="82003352"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="87500168"/>
+        <c:axId val="92660372"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -8770,12 +8770,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40134461"/>
+        <c:crossAx val="82003352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="40134461"/>
+        <c:axId val="82003352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8851,7 +8851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87500168"/>
+        <c:crossAx val="92660372"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9079,58 +9079,58 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>0.261732744185132</c:v>
+                  <c:v>0.261732744185131</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.290113213296011</c:v>
+                  <c:v>0.29011321329601</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.333451909092295</c:v>
+                  <c:v>0.333451909092294</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.374687060217597</c:v>
+                  <c:v>0.374687060217596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.414781377817004</c:v>
+                  <c:v>0.414781377817003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.454109553806323</c:v>
+                  <c:v>0.454109553806322</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.492857199573342</c:v>
+                  <c:v>0.492857199573341</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.531129458085828</c:v>
+                  <c:v>0.531129458085827</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.568991541923245</c:v>
+                  <c:v>0.568991541923244</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.606486767989317</c:v>
+                  <c:v>0.606486767989316</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.64364555794179</c:v>
+                  <c:v>0.643645557941789</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.680490313744652</c:v>
+                  <c:v>0.680490313744651</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.717038227293873</c:v>
+                  <c:v>0.717038227293872</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.753302980127368</c:v>
+                  <c:v>0.753302980127367</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.789295812981246</c:v>
+                  <c:v>0.789295812981245</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.825026221223475</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.860502419800834</c:v>
+                  <c:v>0.860502419800833</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.895731661692378</c:v>
+                  <c:v>0.895731661692377</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0.930720460735534</c:v>
@@ -9546,11 +9546,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="83647709"/>
-        <c:axId val="14761341"/>
+        <c:axId val="56530951"/>
+        <c:axId val="38171844"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="83647709"/>
+        <c:axId val="56530951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9628,12 +9628,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14761341"/>
+        <c:crossAx val="38171844"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="14761341"/>
+        <c:axId val="38171844"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -9711,7 +9711,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83647709"/>
+        <c:crossAx val="56530951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10209,253 +10209,253 @@
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="111"/>
                 <c:pt idx="0">
-                  <c:v>4.12595371875577E-008</c:v>
+                  <c:v>4.12595371875536E-008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4440509614111E-006</c:v>
+                  <c:v>1.44405096141096E-006</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.05910527907022E-005</c:v>
+                  <c:v>4.0591052790698E-005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00093203830167256</c:v>
+                  <c:v>0.000932038301672462</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0176280524713961</c:v>
+                  <c:v>0.0176280524713942</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.277754114572687</c:v>
+                  <c:v>0.277754114572659</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.68479223074768</c:v>
+                  <c:v>3.68479223074734</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>41.5340401083241</c:v>
+                  <c:v>41.5340401083201</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>401.274664027716</c:v>
+                  <c:v>401.27466402768</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3354.98801404925</c:v>
+                  <c:v>3354.98801404896</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24456.7265167271</c:v>
+                  <c:v>24456.7265167251</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>156629.37581588</c:v>
+                  <c:v>156629.375815868</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>887521.144004407</c:v>
+                  <c:v>887521.14400434</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4478844.77418114</c:v>
+                  <c:v>4478844.77418083</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>20272038.0423622</c:v>
+                  <c:v>20272038.0423608</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>82764226.5140739</c:v>
+                  <c:v>82764226.5140686</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>306557393.298656</c:v>
+                  <c:v>306557393.298638</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1035572059.74095</c:v>
+                  <c:v>1035572059.74089</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3206942082.09439</c:v>
+                  <c:v>3206942082.09422</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>9148098150.45453</c:v>
+                  <c:v>9148098150.45407</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>24145781305.8027</c:v>
+                  <c:v>24145781305.8016</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>59215109928.4179</c:v>
+                  <c:v>59215109928.4152</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>135480438821.401</c:v>
+                  <c:v>135480438821.395</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>290286685444.806</c:v>
+                  <c:v>290286685444.794</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>584508954297.728</c:v>
+                  <c:v>584508954297.705</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1109703849105.53</c:v>
+                  <c:v>1109703849105.49</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1992541467247.76</c:v>
+                  <c:v>1992541467247.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>3393781222482.73</c:v>
+                  <c:v>3393781222482.62</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5497513386508.33</c:v>
+                  <c:v>5497513386508.16</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8491745566599.15</c:v>
+                  <c:v>8491745566598.91</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>12537582847949.9</c:v>
+                  <c:v>12537582847949.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>17733172516323.9</c:v>
+                  <c:v>17733172516323.4</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>24080108427770.4</c:v>
+                  <c:v>24080108427769.9</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>31456451546858.3</c:v>
+                  <c:v>31456451546857.6</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>39608523683746.8</c:v>
+                  <c:v>39608523683745.9</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>48162363161980.7</c:v>
+                  <c:v>48162363161979.7</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>56658382086389.3</c:v>
+                  <c:v>56658382086388.3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>64597154864578.6</c:v>
+                  <c:v>64597154864577.4</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>71497913082769.8</c:v>
+                  <c:v>71497913082768.7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>76952984228087.5</c:v>
+                  <c:v>76952984228086.3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>80668893331997.8</c:v>
+                  <c:v>80668893331996.6</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>82492442819656.2</c:v>
+                  <c:v>82492442819655.1</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>82415430805814.3</c:v>
+                  <c:v>82415430805813.2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>80561615772911.3</c:v>
+                  <c:v>80561615772910.4</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>77159765753436.9</c:v>
+                  <c:v>77159765753436</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>72509074323317.1</c:v>
+                  <c:v>72509074323316.3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>66943117635368.8</c:v>
+                  <c:v>66943117635368.1</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>60796768202383.2</c:v>
+                  <c:v>60796768202382.6</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>54379985124458.8</c:v>
+                  <c:v>54379985124458.3</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>47959889115818</c:v>
+                  <c:v>47959889115817.6</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>41751236769013.3</c:v>
+                  <c:v>41751236769013</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>35913071785964.5</c:v>
+                  <c:v>35913071785964.3</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>30552404043955.5</c:v>
+                  <c:v>30552404043955.3</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>25729605406477.8</c:v>
+                  <c:v>25729605406477.6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>21467325468405.1</c:v>
+                  <c:v>21467325468404.9</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>17758803409792.2</c:v>
+                  <c:v>17758803409792.1</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>14576329483703.9</c:v>
+                  <c:v>14576329483703.8</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>11878676861475.4</c:v>
+                  <c:v>11878676861475.3</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>9616882348947.4</c:v>
+                  <c:v>9616882348947.35</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>7739049298030.6</c:v>
+                  <c:v>7739049298030.56</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>6193669889095.34</c:v>
+                  <c:v>6193669889095.31</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>4931942606475.08</c:v>
+                  <c:v>4931942606475.06</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>3909130301667.26</c:v>
+                  <c:v>3909130301667.24</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>3085348152298.03</c:v>
+                  <c:v>3085348152298.02</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>2425729943745.37</c:v>
+                  <c:v>2425729943745.36</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>1900362666610.99</c:v>
+                  <c:v>1900362666610.98</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>1483927915125.46</c:v>
+                  <c:v>1483927915125.45</c:v>
                 </c:pt>
                 <c:pt idx="67">
                   <c:v>1155283631863.61</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>896953645441.247</c:v>
+                  <c:v>896953645441.244</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>694630930880.14</c:v>
+                  <c:v>694630930880.138</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>536697945149.734</c:v>
+                  <c:v>536697945149.732</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>413788286443.935</c:v>
+                  <c:v>413788286443.933</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>318399641040.646</c:v>
+                  <c:v>318399641040.645</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>244557574908.843</c:v>
+                  <c:v>244557574908.842</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>187527631470.364</c:v>
+                  <c:v>187527631470.363</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>143576128688.443</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>109769956502.379</c:v>
+                  <c:v>109769956502.378</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>83814025702.9698</c:v>
+                  <c:v>83814025702.9695</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>63918352884.489</c:v>
+                  <c:v>63918352884.4888</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>48691148028.7492</c:v>
+                  <c:v>48691148028.7491</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>37053302793.9214</c:v>
+                  <c:v>37053302793.9213</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>28170203708.4607</c:v>
+                  <c:v>28170203708.4606</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>21397868960.9361</c:v>
+                  <c:v>21397868960.936</c:v>
                 </c:pt>
                 <c:pt idx="83">
                   <c:v>16240412560.8319</c:v>
@@ -10464,19 +10464,19 @@
                   <c:v>12316749504.1796</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>9334510403.98083</c:v>
+                  <c:v>9334510403.98081</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>7069784053.138</c:v>
+                  <c:v>7069784053.13798</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>5351315428.27379</c:v>
+                  <c:v>5351315428.27377</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>4048307714.306</c:v>
+                  <c:v>4048307714.30599</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>3060997412.88598</c:v>
+                  <c:v>3060997412.88597</c:v>
                 </c:pt>
                 <c:pt idx="90">
                   <c:v>2313369805.58705</c:v>
@@ -10488,22 +10488,22 @@
                   <c:v>1319611580.97545</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>996074758.77383</c:v>
+                  <c:v>996074758.773827</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>751595209.215927</c:v>
+                  <c:v>751595209.215925</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>566935176.452276</c:v>
+                  <c:v>566935176.452274</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>427514041.470436</c:v>
+                  <c:v>427514041.470435</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>322288177.202813</c:v>
+                  <c:v>322288177.202812</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>242898123.41893</c:v>
+                  <c:v>242898123.418929</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>183019671.013909</c:v>
@@ -10512,34 +10512,34 @@
                   <c:v>137870956.46681</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>103837980.487707</c:v>
+                  <c:v>103837980.487706</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>78190599.876553</c:v>
+                  <c:v>78190599.8765527</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>58867242.3936558</c:v>
+                  <c:v>58867242.3936556</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>44311791.9208009</c:v>
+                  <c:v>44311791.9208008</c:v>
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>33350054.4515107</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>25096330.9771608</c:v>
+                  <c:v>25096330.9771607</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>18882732.0912649</c:v>
+                  <c:v>18882732.0912648</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>14205759.2690719</c:v>
+                  <c:v>14205759.2690718</c:v>
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>10685945.350305</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>8037369.74154944</c:v>
+                  <c:v>8037369.74154942</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11286,11 +11286,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="56528756"/>
-        <c:axId val="28913528"/>
+        <c:axId val="89538603"/>
+        <c:axId val="77610986"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="56528756"/>
+        <c:axId val="89538603"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -11367,12 +11367,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28913528"/>
+        <c:crossAx val="77610986"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="28913528"/>
+        <c:axId val="77610986"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -11449,7 +11449,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56528756"/>
+        <c:crossAx val="89538603"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -12104,11 +12104,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="46651933"/>
-        <c:axId val="76463050"/>
+        <c:axId val="18280641"/>
+        <c:axId val="24694388"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="46651933"/>
+        <c:axId val="18280641"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="8"/>
@@ -12186,12 +12186,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76463050"/>
+        <c:crossAx val="24694388"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76463050"/>
+        <c:axId val="24694388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12267,7 +12267,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46651933"/>
+        <c:crossAx val="18280641"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13178,11 +13178,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="51640941"/>
-        <c:axId val="37481122"/>
+        <c:axId val="20723124"/>
+        <c:axId val="48240744"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="51640941"/>
+        <c:axId val="20723124"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13259,12 +13259,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37481122"/>
+        <c:crossAx val="48240744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="37481122"/>
+        <c:axId val="48240744"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -13343,7 +13343,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51640941"/>
+        <c:crossAx val="20723124"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -13982,11 +13982,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="60181612"/>
-        <c:axId val="17782534"/>
+        <c:axId val="22820708"/>
+        <c:axId val="20802901"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="60181612"/>
+        <c:axId val="22820708"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -14063,12 +14063,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17782534"/>
+        <c:crossAx val="20802901"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="17782534"/>
+        <c:axId val="20802901"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -14146,7 +14146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60181612"/>
+        <c:crossAx val="22820708"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -15109,11 +15109,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="8374578"/>
-        <c:axId val="44542293"/>
+        <c:axId val="84649995"/>
+        <c:axId val="25066936"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="8374578"/>
+        <c:axId val="84649995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="3000"/>
@@ -15191,12 +15191,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44542293"/>
+        <c:crossAx val="25066936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="44542293"/>
+        <c:axId val="25066936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15272,7 +15272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8374578"/>
+        <c:crossAx val="84649995"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -16669,11 +16669,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="87443349"/>
-        <c:axId val="36178552"/>
+        <c:axId val="55059221"/>
+        <c:axId val="76718376"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="87443349"/>
+        <c:axId val="55059221"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16750,12 +16750,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36178552"/>
+        <c:crossAx val="76718376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="36178552"/>
+        <c:axId val="76718376"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -16832,7 +16832,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87443349"/>
+        <c:crossAx val="55059221"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -17181,11 +17181,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="97346656"/>
-        <c:axId val="38452845"/>
+        <c:axId val="59433712"/>
+        <c:axId val="52725275"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="97346656"/>
+        <c:axId val="59433712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17261,12 +17261,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38452845"/>
+        <c:crossAx val="52725275"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="38452845"/>
+        <c:axId val="52725275"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17342,7 +17342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97346656"/>
+        <c:crossAx val="59433712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -17691,11 +17691,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="32177355"/>
-        <c:axId val="60273095"/>
+        <c:axId val="21710261"/>
+        <c:axId val="86495050"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32177355"/>
+        <c:axId val="21710261"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17771,12 +17771,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60273095"/>
+        <c:crossAx val="86495050"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="60273095"/>
+        <c:axId val="86495050"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -17854,7 +17854,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32177355"/>
+        <c:crossAx val="21710261"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -18469,11 +18469,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="63769224"/>
-        <c:axId val="75388820"/>
+        <c:axId val="3657001"/>
+        <c:axId val="34372798"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="63769224"/>
+        <c:axId val="3657001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -18549,12 +18549,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75388820"/>
+        <c:crossAx val="34372798"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="75388820"/>
+        <c:axId val="34372798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -18631,7 +18631,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63769224"/>
+        <c:crossAx val="3657001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -24726,11 +24726,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="19191217"/>
-        <c:axId val="16478523"/>
+        <c:axId val="99685741"/>
+        <c:axId val="21964469"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="19191217"/>
+        <c:axId val="99685741"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1000"/>
@@ -24808,12 +24808,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16478523"/>
+        <c:crossAx val="21964469"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="16478523"/>
+        <c:axId val="21964469"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -24889,7 +24889,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19191217"/>
+        <c:crossAx val="99685741"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -26684,11 +26684,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="5788534"/>
-        <c:axId val="31707399"/>
+        <c:axId val="76255405"/>
+        <c:axId val="79026493"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="5788534"/>
+        <c:axId val="76255405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -26764,12 +26764,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31707399"/>
+        <c:crossAx val="79026493"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="31707399"/>
+        <c:axId val="79026493"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -26847,7 +26847,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5788534"/>
+        <c:crossAx val="76255405"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -27988,7 +27988,7 @@
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">$B$6*(0.75*INDEX(Data!$B$4:$B$74,1))^0.25</f>
-        <v>4682.15405820835</v>
+        <v>4682.15405820834</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>60</v>
@@ -28048,7 +28048,7 @@
       </c>
       <c r="B17" s="12" t="n">
         <f aca="false">SUMPRODUCT(T31:T150,U31:U150)/(sigSB*B6^4)</f>
-        <v>1.00452935678744</v>
+        <v>1.00452935678743</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>223</v>
@@ -28077,11 +28077,11 @@
       </c>
       <c r="N20" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M20)/M20,$H$31:$H$101)</f>
-        <v>9012848481041.55</v>
+        <v>9012848481041.4</v>
       </c>
       <c r="O20" s="17" t="n">
         <f aca="false">N20/N40</f>
-        <v>0.261732744185132</v>
+        <v>0.261732744185131</v>
       </c>
       <c r="P20" s="17" t="n">
         <f aca="false">(2+3*M20)/5</f>
@@ -28098,11 +28098,11 @@
       </c>
       <c r="N21" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M21)/M21,$H$31:$H$101)</f>
-        <v>9990138765119.64</v>
+        <v>9990138765119.48</v>
       </c>
       <c r="O21" s="17" t="n">
         <f aca="false">N21/N40</f>
-        <v>0.290113213296011</v>
+        <v>0.29011321329601</v>
       </c>
       <c r="P21" s="17" t="n">
         <f aca="false">(2+3*M21)/5</f>
@@ -28119,11 +28119,11 @@
       </c>
       <c r="N22" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M22)/M22,$H$31:$H$101)</f>
-        <v>11482520239183.8</v>
+        <v>11482520239183.6</v>
       </c>
       <c r="O22" s="17" t="n">
         <f aca="false">N22/N40</f>
-        <v>0.333451909092295</v>
+        <v>0.333451909092294</v>
       </c>
       <c r="P22" s="17" t="n">
         <f aca="false">(2+3*M22)/5</f>
@@ -28140,11 +28140,11 @@
       </c>
       <c r="N23" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M23)/M23,$H$31:$H$101)</f>
-        <v>12902465498009.8</v>
+        <v>12902465498009.6</v>
       </c>
       <c r="O23" s="17" t="n">
         <f aca="false">N23/N40</f>
-        <v>0.374687060217597</v>
+        <v>0.374687060217596</v>
       </c>
       <c r="P23" s="17" t="n">
         <f aca="false">(2+3*M23)/5</f>
@@ -28161,11 +28161,11 @@
       </c>
       <c r="N24" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M24)/M24,$H$31:$H$101)</f>
-        <v>14283125799414.8</v>
+        <v>14283125799414.6</v>
       </c>
       <c r="O24" s="17" t="n">
         <f aca="false">N24/N40</f>
-        <v>0.414781377817004</v>
+        <v>0.414781377817003</v>
       </c>
       <c r="P24" s="17" t="n">
         <f aca="false">(2+3*M24)/5</f>
@@ -28182,11 +28182,11 @@
       </c>
       <c r="N25" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M25)/M25,$H$31:$H$101)</f>
-        <v>15637403776100.6</v>
+        <v>15637403776100.4</v>
       </c>
       <c r="O25" s="17" t="n">
         <f aca="false">N25/N40</f>
-        <v>0.454109553806323</v>
+        <v>0.454109553806322</v>
       </c>
       <c r="P25" s="17" t="n">
         <f aca="false">(2+3*M25)/5</f>
@@ -28203,11 +28203,11 @@
       </c>
       <c r="N26" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M26)/M26,$H$31:$H$101)</f>
-        <v>16971691013956.5</v>
+        <v>16971691013956.2</v>
       </c>
       <c r="O26" s="17" t="n">
         <f aca="false">N26/N40</f>
-        <v>0.492857199573342</v>
+        <v>0.492857199573341</v>
       </c>
       <c r="P26" s="17" t="n">
         <f aca="false">(2+3*M26)/5</f>
@@ -28224,11 +28224,11 @@
       </c>
       <c r="N27" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M27)/M27,$H$31:$H$101)</f>
-        <v>18289608143791.4</v>
+        <v>18289608143791.2</v>
       </c>
       <c r="O27" s="17" t="n">
         <f aca="false">N27/N40</f>
-        <v>0.531129458085828</v>
+        <v>0.531129458085827</v>
       </c>
       <c r="P27" s="17" t="n">
         <f aca="false">(2+3*M27)/5</f>
@@ -28245,11 +28245,11 @@
       </c>
       <c r="N28" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M28)/M28,$H$31:$H$101)</f>
-        <v>19593400781069.4</v>
+        <v>19593400781069.1</v>
       </c>
       <c r="O28" s="17" t="n">
         <f aca="false">N28/N40</f>
-        <v>0.568991541923245</v>
+        <v>0.568991541923244</v>
       </c>
       <c r="P28" s="17" t="n">
         <f aca="false">(2+3*M28)/5</f>
@@ -28266,11 +28266,11 @@
       </c>
       <c r="N29" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M29)/M29,$H$31:$H$101)</f>
-        <v>20884560556847.6</v>
+        <v>20884560556847.4</v>
       </c>
       <c r="O29" s="17" t="n">
         <f aca="false">N29/N40</f>
-        <v>0.606486767989317</v>
+        <v>0.606486767989316</v>
       </c>
       <c r="P29" s="17" t="n">
         <f aca="false">(2+3*M29)/5</f>
@@ -28311,11 +28311,11 @@
       </c>
       <c r="N30" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M30)/M30,$H$31:$H$101)</f>
-        <v>22164135050376</v>
+        <v>22164135050375.7</v>
       </c>
       <c r="O30" s="17" t="n">
         <f aca="false">N30/N40</f>
-        <v>0.64364555794179</v>
+        <v>0.643645557941789</v>
       </c>
       <c r="P30" s="17" t="n">
         <f aca="false">(2+3*M30)/5</f>
@@ -28345,7 +28345,7 @@
       </c>
       <c r="F31" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,1)</f>
-        <v>0.577319523037564</v>
+        <v>0.577319523037558</v>
       </c>
       <c r="G31" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,1)</f>
@@ -28357,7 +28357,7 @@
       </c>
       <c r="I31" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E31+F31))^0.25</f>
-        <v>4682.15405820835</v>
+        <v>4682.15405820834</v>
       </c>
       <c r="J31" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E31+2/3))^0.25</f>
@@ -28365,18 +28365,18 @@
       </c>
       <c r="K31" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I31))-1)</f>
-        <v>8183253589441.24</v>
+        <v>8183253589441.11</v>
       </c>
       <c r="M31" s="16" t="n">
         <v>0.55</v>
       </c>
       <c r="N31" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M31)/M31,$H$31:$H$101)</f>
-        <v>23432895680254.6</v>
+        <v>23432895680254.3</v>
       </c>
       <c r="O31" s="17" t="n">
         <f aca="false">N31/N40</f>
-        <v>0.680490313744652</v>
+        <v>0.680490313744651</v>
       </c>
       <c r="P31" s="17" t="n">
         <f aca="false">(2+3*M31)/5</f>
@@ -28391,7 +28391,7 @@
       </c>
       <c r="T31" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S31*0.000000001)^5/(EXP(hP*cL/(S31*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>2.30912357538745E-013</v>
+        <v>2.30912357538727E-013</v>
       </c>
       <c r="U31" s="23" t="n">
         <f aca="false">(S32-S31)/2*0.000000001</f>
@@ -28409,7 +28409,7 @@
       </c>
       <c r="F32" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,2)</f>
-        <v>0.579055250680859</v>
+        <v>0.579055250680853</v>
       </c>
       <c r="G32" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,2)</f>
@@ -28421,7 +28421,7 @@
       </c>
       <c r="I32" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E32+F32))^0.25</f>
-        <v>4687.69102634296</v>
+        <v>4687.69102634295</v>
       </c>
       <c r="J32" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E32+2/3))^0.25</f>
@@ -28429,18 +28429,18 @@
       </c>
       <c r="K32" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I32))-1)</f>
-        <v>8243002822771.65</v>
+        <v>8243002822771.53</v>
       </c>
       <c r="M32" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="N32" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M32)/M32,$H$31:$H$101)</f>
-        <v>24691434454770.1</v>
+        <v>24691434454769.8</v>
       </c>
       <c r="O32" s="17" t="n">
         <f aca="false">N32/N40</f>
-        <v>0.717038227293873</v>
+        <v>0.717038227293872</v>
       </c>
       <c r="P32" s="17" t="n">
         <f aca="false">(2+3*M32)/5</f>
@@ -28455,7 +28455,7 @@
       </c>
       <c r="T32" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S32*0.000000001)^5/(EXP(hP*cL/(S32*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1.67505523188838E-011</v>
+        <v>1.67505523188824E-011</v>
       </c>
       <c r="U32" s="23" t="n">
         <f aca="false">(S33-S31)/2*0.000000001</f>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,3)</f>
-        <v>0.579285383685983</v>
+        <v>0.579285383685977</v>
       </c>
       <c r="G33" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,3)</f>
@@ -28485,7 +28485,7 @@
       </c>
       <c r="I33" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E33+F33))^0.25</f>
-        <v>4688.48134699371</v>
+        <v>4688.4813469937</v>
       </c>
       <c r="J33" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E33+2/3))^0.25</f>
@@ -28493,18 +28493,18 @@
       </c>
       <c r="K33" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I33))-1)</f>
-        <v>8251555163547.26</v>
+        <v>8251555163547.13</v>
       </c>
       <c r="M33" s="16" t="n">
         <v>0.65</v>
       </c>
       <c r="N33" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M33)/M33,$H$31:$H$101)</f>
-        <v>25940222501937.5</v>
+        <v>25940222501937.2</v>
       </c>
       <c r="O33" s="17" t="n">
         <f aca="false">N33/N40</f>
-        <v>0.753302980127368</v>
+        <v>0.753302980127367</v>
       </c>
       <c r="P33" s="17" t="n">
         <f aca="false">(2+3*M33)/5</f>
@@ -28519,7 +28519,7 @@
       </c>
       <c r="T33" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S33*0.000000001)^5/(EXP(hP*cL/(S33*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>9.38985598810061E-010</v>
+        <v>9.38985598809971E-010</v>
       </c>
       <c r="U33" s="23" t="n">
         <f aca="false">(S34-S32)/2*0.000000001</f>
@@ -28537,7 +28537,7 @@
       </c>
       <c r="F34" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,4)</f>
-        <v>0.579544691018356</v>
+        <v>0.57954469101835</v>
       </c>
       <c r="G34" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,4)</f>
@@ -28549,7 +28549,7 @@
       </c>
       <c r="I34" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E34+F34))^0.25</f>
-        <v>4689.38255750344</v>
+        <v>4689.38255750343</v>
       </c>
       <c r="J34" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E34+2/3))^0.25</f>
@@ -28557,18 +28557,18 @@
       </c>
       <c r="K34" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I34))-1)</f>
-        <v>8261314811199.53</v>
+        <v>8261314811199.4</v>
       </c>
       <c r="M34" s="16" t="n">
         <v>0.7</v>
       </c>
       <c r="N34" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M34)/M34,$H$31:$H$101)</f>
-        <v>27179646900002.1</v>
+        <v>27179646900001.7</v>
       </c>
       <c r="O34" s="17" t="n">
         <f aca="false">N34/N40</f>
-        <v>0.789295812981246</v>
+        <v>0.789295812981245</v>
       </c>
       <c r="P34" s="17" t="n">
         <f aca="false">(2+3*M34)/5</f>
@@ -28583,7 +28583,7 @@
       </c>
       <c r="T34" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S34*0.000000001)^5/(EXP(hP*cL/(S34*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4.12595371875577E-008</v>
+        <v>4.12595371875536E-008</v>
       </c>
       <c r="U34" s="23" t="n">
         <f aca="false">(S35-S33)/2*0.000000001</f>
@@ -28601,7 +28601,7 @@
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,5)</f>
-        <v>0.579836621494636</v>
+        <v>0.57983662149463</v>
       </c>
       <c r="G35" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,5)</f>
@@ -28613,7 +28613,7 @@
       </c>
       <c r="I35" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E35+F35))^0.25</f>
-        <v>4690.40986124708</v>
+        <v>4690.40986124706</v>
       </c>
       <c r="J35" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E35+2/3))^0.25</f>
@@ -28621,14 +28621,14 @@
       </c>
       <c r="K35" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I35))-1)</f>
-        <v>8272449511045.37</v>
+        <v>8272449511045.24</v>
       </c>
       <c r="M35" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="N35" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M35)/M35,$H$31:$H$101)</f>
-        <v>28410034624914.3</v>
+        <v>28410034624913.9</v>
       </c>
       <c r="O35" s="17" t="n">
         <f aca="false">N35/N40</f>
@@ -28647,7 +28647,7 @@
       </c>
       <c r="T35" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S35*0.000000001)^5/(EXP(hP*cL/(S35*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1.4440509614111E-006</v>
+        <v>1.44405096141096E-006</v>
       </c>
       <c r="U35" s="23" t="n">
         <f aca="false">(S36-S34)/2*0.000000001</f>
@@ -28665,7 +28665,7 @@
       </c>
       <c r="F36" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,6)</f>
-        <v>0.580164984214312</v>
+        <v>0.580164984214306</v>
       </c>
       <c r="G36" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,6)</f>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="I36" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E36+F36))^0.25</f>
-        <v>4691.58047834856</v>
+        <v>4691.58047834855</v>
       </c>
       <c r="J36" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E36+2/3))^0.25</f>
@@ -28685,18 +28685,18 @@
       </c>
       <c r="K36" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I36))-1)</f>
-        <v>8285149927615.36</v>
+        <v>8285149927615.21</v>
       </c>
       <c r="M36" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="N36" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M36)/M36,$H$31:$H$101)</f>
-        <v>29631668560922.4</v>
+        <v>29631668560922</v>
       </c>
       <c r="O36" s="17" t="n">
         <f aca="false">N36/N40</f>
-        <v>0.860502419800834</v>
+        <v>0.860502419800833</v>
       </c>
       <c r="P36" s="17" t="n">
         <f aca="false">(2+3*M36)/5</f>
@@ -28711,7 +28711,7 @@
       </c>
       <c r="T36" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S36*0.000000001)^5/(EXP(hP*cL/(S36*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4.05910527907022E-005</v>
+        <v>4.0591052790698E-005</v>
       </c>
       <c r="U36" s="23" t="n">
         <f aca="false">(S37-S35)/2*0.000000001</f>
@@ -28729,7 +28729,7 @@
       </c>
       <c r="F37" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,7)</f>
-        <v>0.580533976909004</v>
+        <v>0.580533976908998</v>
       </c>
       <c r="G37" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,7)</f>
@@ -28741,7 +28741,7 @@
       </c>
       <c r="I37" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E37+F37))^0.25</f>
-        <v>4692.91389989854</v>
+        <v>4692.91389989852</v>
       </c>
       <c r="J37" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E37+2/3))^0.25</f>
@@ -28749,18 +28749,18 @@
       </c>
       <c r="K37" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I37))-1)</f>
-        <v>8299632733567.28</v>
+        <v>8299632733567.15</v>
       </c>
       <c r="M37" s="16" t="n">
         <v>0.85</v>
       </c>
       <c r="N37" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M37)/M37,$H$31:$H$101)</f>
-        <v>30844798466616.8</v>
+        <v>30844798466616.4</v>
       </c>
       <c r="O37" s="17" t="n">
         <f aca="false">N37/N40</f>
-        <v>0.895731661692378</v>
+        <v>0.895731661692377</v>
       </c>
       <c r="P37" s="17" t="n">
         <f aca="false">(2+3*M37)/5</f>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="T37" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S37*0.000000001)^5/(EXP(hP*cL/(S37*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>0.00093203830167256</v>
+        <v>0.000932038301672462</v>
       </c>
       <c r="U37" s="23" t="n">
         <f aca="false">(S38-S36)/2*0.000000001</f>
@@ -28793,7 +28793,7 @@
       </c>
       <c r="F38" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,8)</f>
-        <v>0.580948214567638</v>
+        <v>0.580948214567632</v>
       </c>
       <c r="G38" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,8)</f>
@@ -28805,7 +28805,7 @@
       </c>
       <c r="I38" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E38+F38))^0.25</f>
-        <v>4694.43217149548</v>
+        <v>4694.43217149547</v>
       </c>
       <c r="J38" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E38+2/3))^0.25</f>
@@ -28813,14 +28813,14 @@
       </c>
       <c r="K38" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I38))-1)</f>
-        <v>8316144114897.12</v>
+        <v>8316144114896.99</v>
       </c>
       <c r="M38" s="16" t="n">
         <v>0.9</v>
       </c>
       <c r="N38" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M38)/M38,$H$31:$H$101)</f>
-        <v>32049648648016</v>
+        <v>32049648648015.6</v>
       </c>
       <c r="O38" s="17" t="n">
         <f aca="false">N38/N40</f>
@@ -28839,7 +28839,7 @@
       </c>
       <c r="T38" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S38*0.000000001)^5/(EXP(hP*cL/(S38*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>0.0176280524713961</v>
+        <v>0.0176280524713942</v>
       </c>
       <c r="U38" s="23" t="n">
         <f aca="false">(S39-S37)/2*0.000000001</f>
@@ -28857,7 +28857,7 @@
       </c>
       <c r="F39" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,9)</f>
-        <v>0.581412757823075</v>
+        <v>0.581412757823069</v>
       </c>
       <c r="G39" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,9)</f>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="I39" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E39+F39))^0.25</f>
-        <v>4696.16020890835</v>
+        <v>4696.16020890834</v>
       </c>
       <c r="J39" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E39+2/3))^0.25</f>
@@ -28877,14 +28877,14 @@
       </c>
       <c r="K39" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I39))-1)</f>
-        <v>8334963750608.97</v>
+        <v>8334963750608.84</v>
       </c>
       <c r="M39" s="16" t="n">
         <v>0.95</v>
       </c>
       <c r="N39" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M39)/M39,$H$31:$H$101)</f>
-        <v>33246423431715.4</v>
+        <v>33246423431715</v>
       </c>
       <c r="O39" s="17" t="n">
         <f aca="false">N39/N40</f>
@@ -28903,7 +28903,7 @@
       </c>
       <c r="T39" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S39*0.000000001)^5/(EXP(hP*cL/(S39*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>0.277754114572687</v>
+        <v>0.277754114572659</v>
       </c>
       <c r="U39" s="23" t="n">
         <f aca="false">(S40-S38)/2*0.000000001</f>
@@ -28921,7 +28921,7 @@
       </c>
       <c r="F40" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,10)</f>
-        <v>0.581933140447196</v>
+        <v>0.58193314044719</v>
       </c>
       <c r="G40" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,10)</f>
@@ -28933,7 +28933,7 @@
       </c>
       <c r="I40" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E40+F40))^0.25</f>
-        <v>4698.12614879112</v>
+        <v>4698.1261487911</v>
       </c>
       <c r="J40" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E40+2/3))^0.25</f>
@@ -28941,14 +28941,14 @@
       </c>
       <c r="K40" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I40))-1)</f>
-        <v>8356409333994.65</v>
+        <v>8356409333994.5</v>
       </c>
       <c r="M40" s="16" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="23" t="n">
         <f aca="false">SUMPRODUCT($K$31:$K$101,EXP(-$E$31:$E$101/M40)/M40,$H$31:$H$101)</f>
-        <v>34435311138091.5</v>
+        <v>34435311138091.1</v>
       </c>
       <c r="O40" s="17" t="n">
         <f aca="false">N40/N40</f>
@@ -28967,7 +28967,7 @@
       </c>
       <c r="T40" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S40*0.000000001)^5/(EXP(hP*cL/(S40*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3.68479223074768</v>
+        <v>3.68479223074734</v>
       </c>
       <c r="U40" s="23" t="n">
         <f aca="false">(S41-S39)/2*0.000000001</f>
@@ -28985,7 +28985,7 @@
       </c>
       <c r="F41" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,11)</f>
-        <v>0.582515395139863</v>
+        <v>0.582515395139857</v>
       </c>
       <c r="G41" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,11)</f>
@@ -28997,7 +28997,7 @@
       </c>
       <c r="I41" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E41+F41))^0.25</f>
-        <v>4700.36173748223</v>
+        <v>4700.36173748222</v>
       </c>
       <c r="J41" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E41+2/3))^0.25</f>
@@ -29005,14 +29005,14 @@
       </c>
       <c r="K41" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I41))-1)</f>
-        <v>8380841713294.82</v>
+        <v>8380841713294.7</v>
       </c>
       <c r="S41" s="22" t="n">
         <v>40.914</v>
       </c>
       <c r="T41" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S41*0.000000001)^5/(EXP(hP*cL/(S41*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>41.5340401083241</v>
+        <v>41.5340401083201</v>
       </c>
       <c r="U41" s="23" t="n">
         <f aca="false">(S42-S40)/2*0.000000001</f>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="F42" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,12)</f>
-        <v>0.583166076610894</v>
+        <v>0.583166076610888</v>
       </c>
       <c r="G42" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,12)</f>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="I42" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E42+F42))^0.25</f>
-        <v>4702.90276098299</v>
+        <v>4702.90276098297</v>
       </c>
       <c r="J42" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E42+2/3))^0.25</f>
@@ -29050,14 +29050,14 @@
       </c>
       <c r="K42" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I42))-1)</f>
-        <v>8408670742107.44</v>
+        <v>8408670742107.31</v>
       </c>
       <c r="S42" s="22" t="n">
         <v>43.949</v>
       </c>
       <c r="T42" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S42*0.000000001)^5/(EXP(hP*cL/(S42*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>401.274664027716</v>
+        <v>401.27466402768</v>
       </c>
       <c r="U42" s="23" t="n">
         <f aca="false">(S43-S41)/2*0.000000001</f>
@@ -29075,7 +29075,7 @@
       </c>
       <c r="F43" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,13)</f>
-        <v>0.583892151149632</v>
+        <v>0.583892151149625</v>
       </c>
       <c r="G43" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,13)</f>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="I43" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E43+F43))^0.25</f>
-        <v>4705.78926039965</v>
+        <v>4705.78926039964</v>
       </c>
       <c r="J43" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E43+2/3))^0.25</f>
@@ -29095,14 +29095,14 @@
       </c>
       <c r="K43" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I43))-1)</f>
-        <v>8440359099992.02</v>
+        <v>8440359099991.86</v>
       </c>
       <c r="S43" s="22" t="n">
         <v>47.21</v>
       </c>
       <c r="T43" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S43*0.000000001)^5/(EXP(hP*cL/(S43*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3354.98801404925</v>
+        <v>3354.98801404896</v>
       </c>
       <c r="U43" s="23" t="n">
         <f aca="false">(S44-S42)/2*0.000000001</f>
@@ -29120,7 +29120,7 @@
       </c>
       <c r="F44" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,14)</f>
-        <v>0.584701246853153</v>
+        <v>0.584701246853147</v>
       </c>
       <c r="G44" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,14)</f>
@@ -29132,7 +29132,7 @@
       </c>
       <c r="I44" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E44+F44))^0.25</f>
-        <v>4709.06652742572</v>
+        <v>4709.0665274257</v>
       </c>
       <c r="J44" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E44+2/3))^0.25</f>
@@ -29140,14 +29140,14 @@
       </c>
       <c r="K44" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I44))-1)</f>
-        <v>8476435079653.66</v>
+        <v>8476435079653.54</v>
       </c>
       <c r="S44" s="22" t="n">
         <v>50.713</v>
       </c>
       <c r="T44" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S44*0.000000001)^5/(EXP(hP*cL/(S44*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>24456.7265167271</v>
+        <v>24456.7265167251</v>
       </c>
       <c r="U44" s="23" t="n">
         <f aca="false">(S45-S43)/2*0.000000001</f>
@@ -29165,7 +29165,7 @@
       </c>
       <c r="F45" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,15)</f>
-        <v>0.585601646526454</v>
+        <v>0.585601646526448</v>
       </c>
       <c r="G45" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,15)</f>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="I45" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E45+F45))^0.25</f>
-        <v>4712.78564684139</v>
+        <v>4712.78564684137</v>
       </c>
       <c r="J45" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E45+2/3))^0.25</f>
@@ -29185,14 +29185,14 @@
       </c>
       <c r="K45" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I45))-1)</f>
-        <v>8517500977990.27</v>
+        <v>8517500977990.15</v>
       </c>
       <c r="S45" s="22" t="n">
         <v>54.476</v>
       </c>
       <c r="T45" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S45*0.000000001)^5/(EXP(hP*cL/(S45*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>156629.37581588</v>
+        <v>156629.375815868</v>
       </c>
       <c r="U45" s="23" t="n">
         <f aca="false">(S46-S44)/2*0.000000001</f>
@@ -29210,7 +29210,7 @@
       </c>
       <c r="F46" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,16)</f>
-        <v>0.586602104365434</v>
+        <v>0.586602104365428</v>
       </c>
       <c r="G46" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,16)</f>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="I46" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E46+F46))^0.25</f>
-        <v>4717.00376002962</v>
+        <v>4717.0037600296</v>
       </c>
       <c r="J46" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E46+2/3))^0.25</f>
@@ -29230,14 +29230,14 @@
       </c>
       <c r="K46" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I46))-1)</f>
-        <v>8564239063444.03</v>
+        <v>8564239063443.9</v>
       </c>
       <c r="S46" s="22" t="n">
         <v>58.518</v>
       </c>
       <c r="T46" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S46*0.000000001)^5/(EXP(hP*cL/(S46*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>887521.144004407</v>
+        <v>887521.14400434</v>
       </c>
       <c r="U46" s="23" t="n">
         <f aca="false">(S47-S45)/2*0.000000001</f>
@@ -29255,7 +29255,7 @@
       </c>
       <c r="F47" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,17)</f>
-        <v>0.58771191687879</v>
+        <v>0.587711916878784</v>
       </c>
       <c r="G47" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,17)</f>
@@ -29267,7 +29267,7 @@
       </c>
       <c r="I47" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E47+F47))^0.25</f>
-        <v>4721.78491423875</v>
+        <v>4721.78491423873</v>
       </c>
       <c r="J47" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E47+2/3))^0.25</f>
@@ -29275,14 +29275,14 @@
       </c>
       <c r="K47" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I47))-1)</f>
-        <v>8617424828920.72</v>
+        <v>8617424828920.59</v>
       </c>
       <c r="S47" s="22" t="n">
         <v>62.859</v>
       </c>
       <c r="T47" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S47*0.000000001)^5/(EXP(hP*cL/(S47*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4478844.77418114</v>
+        <v>4478844.77418083</v>
       </c>
       <c r="U47" s="23" t="n">
         <f aca="false">(S48-S46)/2*0.000000001</f>
@@ -29300,7 +29300,7 @@
       </c>
       <c r="F48" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,18)</f>
-        <v>0.58894089452217</v>
+        <v>0.588940894522163</v>
       </c>
       <c r="G48" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,18)</f>
@@ -29312,7 +29312,7 @@
       </c>
       <c r="I48" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E48+F48))^0.25</f>
-        <v>4727.20079794397</v>
+        <v>4727.20079794396</v>
       </c>
       <c r="J48" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E48+2/3))^0.25</f>
@@ -29320,14 +29320,14 @@
       </c>
       <c r="K48" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I48))-1)</f>
-        <v>8677940067877.95</v>
+        <v>8677940067877.81</v>
       </c>
       <c r="S48" s="22" t="n">
         <v>67.523</v>
       </c>
       <c r="T48" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S48*0.000000001)^5/(EXP(hP*cL/(S48*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>20272038.0423622</v>
+        <v>20272038.0423608</v>
       </c>
       <c r="U48" s="23" t="n">
         <f aca="false">(S49-S47)/2*0.000000001</f>
@@ -29345,7 +29345,7 @@
       </c>
       <c r="F49" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,19)</f>
-        <v>0.590299316202863</v>
+        <v>0.590299316202856</v>
       </c>
       <c r="G49" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,19)</f>
@@ -29357,7 +29357,7 @@
       </c>
       <c r="I49" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E49+F49))^0.25</f>
-        <v>4733.331533474</v>
+        <v>4733.33153347399</v>
       </c>
       <c r="J49" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E49+2/3))^0.25</f>
@@ -29365,14 +29365,14 @@
       </c>
       <c r="K49" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I49))-1)</f>
-        <v>8746787924244.2</v>
+        <v>8746787924244.06</v>
       </c>
       <c r="S49" s="22" t="n">
         <v>72.533</v>
       </c>
       <c r="T49" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S49*0.000000001)^5/(EXP(hP*cL/(S49*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>82764226.5140739</v>
+        <v>82764226.5140686</v>
       </c>
       <c r="U49" s="23" t="n">
         <f aca="false">(S50-S48)/2*0.000000001</f>
@@ -29390,7 +29390,7 @@
       </c>
       <c r="F50" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,20)</f>
-        <v>0.591797863318852</v>
+        <v>0.591797863318846</v>
       </c>
       <c r="G50" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,20)</f>
@@ -29402,7 +29402,7 @@
       </c>
       <c r="I50" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E50+F50))^0.25</f>
-        <v>4740.26652664715</v>
+        <v>4740.26652664714</v>
       </c>
       <c r="J50" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E50+2/3))^0.25</f>
@@ -29410,14 +29410,14 @@
       </c>
       <c r="K50" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I50))-1)</f>
-        <v>8825110252110.8</v>
+        <v>8825110252110.63</v>
       </c>
       <c r="S50" s="22" t="n">
         <v>77.915</v>
       </c>
       <c r="T50" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S50*0.000000001)^5/(EXP(hP*cL/(S50*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>306557393.298656</v>
+        <v>306557393.298638</v>
       </c>
       <c r="U50" s="23" t="n">
         <f aca="false">(S51-S49)/2*0.000000001</f>
@@ -29435,7 +29435,7 @@
       </c>
       <c r="F51" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,21)</f>
-        <v>0.59344752968076</v>
+        <v>0.593447529680754</v>
       </c>
       <c r="G51" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,21)</f>
@@ -29447,7 +29447,7 @@
       </c>
       <c r="I51" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E51+F51))^0.25</f>
-        <v>4748.10537185658</v>
+        <v>4748.10537185657</v>
       </c>
       <c r="J51" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E51+2/3))^0.25</f>
@@ -29455,14 +29455,14 @@
       </c>
       <c r="K51" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I51))-1)</f>
-        <v>8914207685206.81</v>
+        <v>8914207685206.66</v>
       </c>
       <c r="S51" s="22" t="n">
         <v>83.696</v>
       </c>
       <c r="T51" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S51*0.000000001)^5/(EXP(hP*cL/(S51*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1035572059.74095</v>
+        <v>1035572059.74089</v>
       </c>
       <c r="U51" s="23" t="n">
         <f aca="false">(S52-S50)/2*0.000000001</f>
@@ -29480,7 +29480,7 @@
       </c>
       <c r="F52" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,22)</f>
-        <v>0.595259503394157</v>
+        <v>0.595259503394151</v>
       </c>
       <c r="G52" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,22)</f>
@@ -29492,7 +29492,7 @@
       </c>
       <c r="I52" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E52+F52))^0.25</f>
-        <v>4756.95880944098</v>
+        <v>4756.95880944096</v>
       </c>
       <c r="J52" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E52+2/3))^0.25</f>
@@ -29500,14 +29500,14 @@
       </c>
       <c r="K52" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I52))-1)</f>
-        <v>9015562892819.57</v>
+        <v>9015562892819.43</v>
       </c>
       <c r="S52" s="22" t="n">
         <v>89.906</v>
       </c>
       <c r="T52" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S52*0.000000001)^5/(EXP(hP*cL/(S52*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3206942082.09439</v>
+        <v>3206942082.09422</v>
       </c>
       <c r="U52" s="23" t="n">
         <f aca="false">(S53-S51)/2*0.000000001</f>
@@ -29525,7 +29525,7 @@
       </c>
       <c r="F53" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,23)</f>
-        <v>0.597245016583342</v>
+        <v>0.597245016583336</v>
       </c>
       <c r="G53" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,23)</f>
@@ -29537,7 +29537,7 @@
       </c>
       <c r="I53" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E53+F53))^0.25</f>
-        <v>4766.94973025255</v>
+        <v>4766.94973025254</v>
       </c>
       <c r="J53" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E53+2/3))^0.25</f>
@@ -29545,14 +29545,14 @@
       </c>
       <c r="K53" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I53))-1)</f>
-        <v>9130867590226.74</v>
+        <v>9130867590226.6</v>
       </c>
       <c r="S53" s="22" t="n">
         <v>96.577</v>
       </c>
       <c r="T53" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S53*0.000000001)^5/(EXP(hP*cL/(S53*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>9148098150.45453</v>
+        <v>9148098150.45407</v>
       </c>
       <c r="U53" s="23" t="n">
         <f aca="false">(S54-S52)/2*0.000000001</f>
@@ -29570,7 +29570,7 @@
       </c>
       <c r="F54" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,24)</f>
-        <v>0.599415158755064</v>
+        <v>0.599415158755058</v>
       </c>
       <c r="G54" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,24)</f>
@@ -29582,7 +29582,7 @@
       </c>
       <c r="I54" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E54+F54))^0.25</f>
-        <v>4778.21422007525</v>
+        <v>4778.21422007524</v>
       </c>
       <c r="J54" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E54+2/3))^0.25</f>
@@ -29590,14 +29590,14 @@
       </c>
       <c r="K54" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I54))-1)</f>
-        <v>9262053980226.12</v>
+        <v>9262053980225.98</v>
       </c>
       <c r="S54" s="22" t="n">
         <v>103.743</v>
       </c>
       <c r="T54" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S54*0.000000001)^5/(EXP(hP*cL/(S54*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>24145781305.8027</v>
+        <v>24145781305.8016</v>
       </c>
       <c r="U54" s="23" t="n">
         <f aca="false">(S55-S53)/2*0.000000001</f>
@@ -29615,7 +29615,7 @@
       </c>
       <c r="F55" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,25)</f>
-        <v>0.601780649680794</v>
+        <v>0.601780649680787</v>
       </c>
       <c r="G55" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,25)</f>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="I55" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E55+F55))^0.25</f>
-        <v>4790.9026339536</v>
+        <v>4790.90263395359</v>
       </c>
       <c r="J55" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E55+2/3))^0.25</f>
@@ -29635,14 +29635,14 @@
       </c>
       <c r="K55" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I55))-1)</f>
-        <v>9411331430466.46</v>
+        <v>9411331430466.29</v>
       </c>
       <c r="S55" s="22" t="n">
         <v>111.44</v>
       </c>
       <c r="T55" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S55*0.000000001)^5/(EXP(hP*cL/(S55*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>59215109928.4179</v>
+        <v>59215109928.4152</v>
       </c>
       <c r="U55" s="23" t="n">
         <f aca="false">(S56-S54)/2*0.000000001</f>
@@ -29660,7 +29660,7 @@
       </c>
       <c r="F56" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,26)</f>
-        <v>0.604351567979417</v>
+        <v>0.604351567979411</v>
       </c>
       <c r="G56" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,26)</f>
@@ -29672,7 +29672,7 @@
       </c>
       <c r="I56" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E56+F56))^0.25</f>
-        <v>4805.18068758967</v>
+        <v>4805.18068758965</v>
       </c>
       <c r="J56" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E56+2/3))^0.25</f>
@@ -29680,14 +29680,14 @@
       </c>
       <c r="K56" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I56))-1)</f>
-        <v>9581229341474.33</v>
+        <v>9581229341474.18</v>
       </c>
       <c r="S56" s="22" t="n">
         <v>119.708</v>
       </c>
       <c r="T56" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S56*0.000000001)^5/(EXP(hP*cL/(S56*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>135480438821.401</v>
+        <v>135480438821.395</v>
       </c>
       <c r="U56" s="23" t="n">
         <f aca="false">(S57-S55)/2*0.000000001</f>
@@ -29705,7 +29705,7 @@
       </c>
       <c r="F57" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,27)</f>
-        <v>0.607137032181322</v>
+        <v>0.607137032181315</v>
       </c>
       <c r="G57" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,27)</f>
@@ -29717,7 +29717,7 @@
       </c>
       <c r="I57" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E57+F57))^0.25</f>
-        <v>4821.23054979749</v>
+        <v>4821.23054979748</v>
       </c>
       <c r="J57" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E57+2/3))^0.25</f>
@@ -29725,14 +29725,14 @@
       </c>
       <c r="K57" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I57))-1)</f>
-        <v>9774647334792.98</v>
+        <v>9774647334792.81</v>
       </c>
       <c r="S57" s="22" t="n">
         <v>128.59</v>
       </c>
       <c r="T57" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S57*0.000000001)^5/(EXP(hP*cL/(S57*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>290286685444.806</v>
+        <v>290286685444.794</v>
       </c>
       <c r="U57" s="23" t="n">
         <f aca="false">(S58-S56)/2*0.000000001</f>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="F58" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,28)</f>
-        <v>0.610143233826245</v>
+        <v>0.610143233826238</v>
       </c>
       <c r="G58" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,28)</f>
@@ -29762,7 +29762,7 @@
       </c>
       <c r="I58" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E58+F58))^0.25</f>
-        <v>4839.24898166427</v>
+        <v>4839.24898166426</v>
       </c>
       <c r="J58" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E58+2/3))^0.25</f>
@@ -29770,14 +29770,14 @@
       </c>
       <c r="K58" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I58))-1)</f>
-        <v>9994877951156.6</v>
+        <v>9994877951156.44</v>
       </c>
       <c r="S58" s="22" t="n">
         <v>138.131</v>
       </c>
       <c r="T58" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S58*0.000000001)^5/(EXP(hP*cL/(S58*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>584508954297.728</v>
+        <v>584508954297.705</v>
       </c>
       <c r="U58" s="23" t="n">
         <f aca="false">(S59-S57)/2*0.000000001</f>
@@ -29795,7 +29795,7 @@
       </c>
       <c r="F59" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,29)</f>
-        <v>0.613377262589377</v>
+        <v>0.61337726258937</v>
       </c>
       <c r="G59" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,29)</f>
@@ -29807,7 +29807,7 @@
       </c>
       <c r="I59" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E59+F59))^0.25</f>
-        <v>4859.45624949731</v>
+        <v>4859.4562494973</v>
       </c>
       <c r="J59" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E59+2/3))^0.25</f>
@@ -29815,14 +29815,14 @@
       </c>
       <c r="K59" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I59))-1)</f>
-        <v>10245771331467.3</v>
+        <v>10245771331467.1</v>
       </c>
       <c r="S59" s="22" t="n">
         <v>148.38</v>
       </c>
       <c r="T59" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S59*0.000000001)^5/(EXP(hP*cL/(S59*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1109703849105.53</v>
+        <v>1109703849105.49</v>
       </c>
       <c r="U59" s="23" t="n">
         <f aca="false">(S60-S58)/2*0.000000001</f>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="F60" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,30)</f>
-        <v>0.616842988473331</v>
+        <v>0.616842988473324</v>
       </c>
       <c r="G60" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,30)</f>
@@ -29852,7 +29852,7 @@
       </c>
       <c r="I60" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E60+F60))^0.25</f>
-        <v>4882.09026824236</v>
+        <v>4882.09026824235</v>
       </c>
       <c r="J60" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E60+2/3))^0.25</f>
@@ -29860,14 +29860,14 @@
       </c>
       <c r="K60" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I60))-1)</f>
-        <v>10531734246731.1</v>
+        <v>10531734246730.9</v>
       </c>
       <c r="S60" s="22" t="n">
         <v>159.389</v>
       </c>
       <c r="T60" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S60*0.000000001)^5/(EXP(hP*cL/(S60*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1992541467247.76</v>
+        <v>1992541467247.7</v>
       </c>
       <c r="U60" s="23" t="n">
         <f aca="false">(S61-S59)/2*0.000000001</f>
@@ -29885,7 +29885,7 @@
       </c>
       <c r="F61" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,31)</f>
-        <v>0.62054143628366</v>
+        <v>0.620541436283652</v>
       </c>
       <c r="G61" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,31)</f>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="I61" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E61+F61))^0.25</f>
-        <v>4907.40914964674</v>
+        <v>4907.40914964673</v>
       </c>
       <c r="J61" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E61+2/3))^0.25</f>
@@ -29905,14 +29905,14 @@
       </c>
       <c r="K61" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I61))-1)</f>
-        <v>10857845159030.2</v>
+        <v>10857845159030</v>
       </c>
       <c r="S61" s="22" t="n">
         <v>171.216</v>
       </c>
       <c r="T61" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S61*0.000000001)^5/(EXP(hP*cL/(S61*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3393781222482.73</v>
+        <v>3393781222482.62</v>
       </c>
       <c r="U61" s="23" t="n">
         <f aca="false">(S62-S60)/2*0.000000001</f>
@@ -29930,7 +29930,7 @@
       </c>
       <c r="F62" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,32)</f>
-        <v>0.624470347888569</v>
+        <v>0.624470347888562</v>
       </c>
       <c r="G62" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,32)</f>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="I62" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E62+F62))^0.25</f>
-        <v>4935.69215633088</v>
+        <v>4935.69215633087</v>
       </c>
       <c r="J62" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E62+2/3))^0.25</f>
@@ -29950,14 +29950,14 @@
       </c>
       <c r="K62" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I62))-1)</f>
-        <v>11229968421224.7</v>
+        <v>11229968421224.5</v>
       </c>
       <c r="S62" s="22" t="n">
         <v>183.919</v>
       </c>
       <c r="T62" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S62*0.000000001)^5/(EXP(hP*cL/(S62*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>5497513386508.33</v>
+        <v>5497513386508.16</v>
       </c>
       <c r="U62" s="23" t="n">
         <f aca="false">(S63-S61)/2*0.000000001</f>
@@ -29975,7 +29975,7 @@
       </c>
       <c r="F63" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,33)</f>
-        <v>0.628623608127862</v>
+        <v>0.628623608127855</v>
       </c>
       <c r="G63" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,33)</f>
@@ -29987,7 +29987,7 @@
       </c>
       <c r="I63" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E63+F63))^0.25</f>
-        <v>4967.24028701626</v>
+        <v>4967.24028701624</v>
       </c>
       <c r="J63" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E63+2/3))^0.25</f>
@@ -29995,14 +29995,14 @@
       </c>
       <c r="K63" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I63))-1)</f>
-        <v>11654885128878.2</v>
+        <v>11654885128878</v>
       </c>
       <c r="S63" s="22" t="n">
         <v>197.565</v>
       </c>
       <c r="T63" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S63*0.000000001)^5/(EXP(hP*cL/(S63*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>8491745566599.15</v>
+        <v>8491745566598.91</v>
       </c>
       <c r="U63" s="23" t="n">
         <f aca="false">(S64-S62)/2*0.000000001</f>
@@ -30020,7 +30020,7 @@
       </c>
       <c r="F64" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,34)</f>
-        <v>0.632990663865204</v>
+        <v>0.632990663865196</v>
       </c>
       <c r="G64" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,34)</f>
@@ -30032,7 +30032,7 @@
       </c>
       <c r="I64" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E64+F64))^0.25</f>
-        <v>5002.37666485136</v>
+        <v>5002.37666485134</v>
       </c>
       <c r="J64" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E64+2/3))^0.25</f>
@@ -30040,14 +30040,14 @@
       </c>
       <c r="K64" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I64))-1)</f>
-        <v>12140446086785.3</v>
+        <v>12140446086785.1</v>
       </c>
       <c r="S64" s="22" t="n">
         <v>212.224</v>
       </c>
       <c r="T64" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S64*0.000000001)^5/(EXP(hP*cL/(S64*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>12537582847949.9</v>
+        <v>12537582847949.5</v>
       </c>
       <c r="U64" s="23" t="n">
         <f aca="false">(S65-S63)/2*0.000000001</f>
@@ -30065,7 +30065,7 @@
       </c>
       <c r="F65" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,35)</f>
-        <v>0.637555960560158</v>
+        <v>0.63755596056015</v>
       </c>
       <c r="G65" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,35)</f>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="I65" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E65+F65))^0.25</f>
-        <v>5041.44669287679</v>
+        <v>5041.44669287678</v>
       </c>
       <c r="J65" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E65+2/3))^0.25</f>
@@ -30085,14 +30085,14 @@
       </c>
       <c r="K65" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I65))-1)</f>
-        <v>12695750060644.3</v>
+        <v>12695750060644.1</v>
       </c>
       <c r="S65" s="22" t="n">
         <v>227.97</v>
       </c>
       <c r="T65" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S65*0.000000001)^5/(EXP(hP*cL/(S65*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>17733172516323.9</v>
+        <v>17733172516323.4</v>
       </c>
       <c r="U65" s="23" t="n">
         <f aca="false">(S66-S64)/2*0.000000001</f>
@@ -30110,7 +30110,7 @@
       </c>
       <c r="F66" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,36)</f>
-        <v>0.642298428241314</v>
+        <v>0.642298428241305</v>
       </c>
       <c r="G66" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,36)</f>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="I66" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E66+F66))^0.25</f>
-        <v>5084.81794107236</v>
+        <v>5084.81794107234</v>
       </c>
       <c r="J66" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E66+2/3))^0.25</f>
@@ -30130,14 +30130,14 @@
       </c>
       <c r="K66" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I66))-1)</f>
-        <v>13331350615269.4</v>
+        <v>13331350615269.2</v>
       </c>
       <c r="S66" s="22" t="n">
         <v>244.885</v>
       </c>
       <c r="T66" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S66*0.000000001)^5/(EXP(hP*cL/(S66*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>24080108427770.4</v>
+        <v>24080108427769.9</v>
       </c>
       <c r="U66" s="23" t="n">
         <f aca="false">(S67-S65)/2*0.000000001</f>
@@ -30155,7 +30155,7 @@
       </c>
       <c r="F67" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,37)</f>
-        <v>0.647191056996101</v>
+        <v>0.647191056996092</v>
       </c>
       <c r="G67" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,37)</f>
@@ -30167,7 +30167,7 @@
       </c>
       <c r="I67" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E67+F67))^0.25</f>
-        <v>5132.87973068102</v>
+        <v>5132.87973068101</v>
       </c>
       <c r="J67" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E67+2/3))^0.25</f>
@@ -30175,14 +30175,14 @@
       </c>
       <c r="K67" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I67))-1)</f>
-        <v>14059494818691.3</v>
+        <v>14059494818691.1</v>
       </c>
       <c r="S67" s="22" t="n">
         <v>263.055</v>
       </c>
       <c r="T67" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S67*0.000000001)^5/(EXP(hP*cL/(S67*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>31456451546858.3</v>
+        <v>31456451546857.6</v>
       </c>
       <c r="U67" s="23" t="n">
         <f aca="false">(S68-S66)/2*0.000000001</f>
@@ -30200,7 +30200,7 @@
       </c>
       <c r="F68" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,38)</f>
-        <v>0.652200610629809</v>
+        <v>0.6522006106298</v>
       </c>
       <c r="G68" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,38)</f>
@@ -30212,7 +30212,7 @@
       </c>
       <c r="I68" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E68+F68))^0.25</f>
-        <v>5186.04238344752</v>
+        <v>5186.04238344751</v>
       </c>
       <c r="J68" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E68+2/3))^0.25</f>
@@ -30220,14 +30220,14 @@
       </c>
       <c r="K68" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I68))-1)</f>
-        <v>14894396838539.8</v>
+        <v>14894396838539.6</v>
       </c>
       <c r="S68" s="22" t="n">
         <v>282.573</v>
       </c>
       <c r="T68" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S68*0.000000001)^5/(EXP(hP*cL/(S68*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>39608523683746.8</v>
+        <v>39608523683745.9</v>
       </c>
       <c r="U68" s="23" t="n">
         <f aca="false">(S69-S67)/2*0.000000001</f>
@@ -30245,7 +30245,7 @@
       </c>
       <c r="F69" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,39)</f>
-        <v>0.657287535272701</v>
+        <v>0.657287535272691</v>
       </c>
       <c r="G69" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,39)</f>
@@ -30257,7 +30257,7 @@
       </c>
       <c r="I69" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E69+F69))^0.25</f>
-        <v>5244.73610581189</v>
+        <v>5244.73610581188</v>
       </c>
       <c r="J69" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E69+2/3))^0.25</f>
@@ -30265,14 +30265,14 @@
       </c>
       <c r="K69" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I69))-1)</f>
-        <v>15852548875513.4</v>
+        <v>15852548875513.2</v>
       </c>
       <c r="S69" s="22" t="n">
         <v>303.538</v>
       </c>
       <c r="T69" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S69*0.000000001)^5/(EXP(hP*cL/(S69*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>48162363161980.7</v>
+        <v>48162363161979.7</v>
       </c>
       <c r="U69" s="23" t="n">
         <f aca="false">(S70-S68)/2*0.000000001</f>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="F70" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,40)</f>
-        <v>0.662406126341922</v>
+        <v>0.662406126341912</v>
       </c>
       <c r="G70" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,40)</f>
@@ -30302,7 +30302,7 @@
       </c>
       <c r="I70" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E70+F70))^0.25</f>
-        <v>5309.40948073326</v>
+        <v>5309.40948073325</v>
       </c>
       <c r="J70" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E70+2/3))^0.25</f>
@@ -30310,14 +30310,14 @@
       </c>
       <c r="K70" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I70))-1)</f>
-        <v>16953070852362.2</v>
+        <v>16953070852361.9</v>
       </c>
       <c r="S70" s="22" t="n">
         <v>326.06</v>
       </c>
       <c r="T70" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S70*0.000000001)^5/(EXP(hP*cL/(S70*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>56658382086389.3</v>
+        <v>56658382086388.3</v>
       </c>
       <c r="U70" s="23" t="n">
         <f aca="false">(S71-S69)/2*0.000000001</f>
@@ -30335,7 +30335,7 @@
       </c>
       <c r="F71" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,41)</f>
-        <v>0.667505020846813</v>
+        <v>0.667505020846802</v>
       </c>
       <c r="G71" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,41)</f>
@@ -30347,7 +30347,7 @@
       </c>
       <c r="I71" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E71+F71))^0.25</f>
-        <v>5380.52754258322</v>
+        <v>5380.52754258321</v>
       </c>
       <c r="J71" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E71+2/3))^0.25</f>
@@ -30355,14 +30355,14 @@
       </c>
       <c r="K71" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I71))-1)</f>
-        <v>18218098676776.6</v>
+        <v>18218098676776.3</v>
       </c>
       <c r="S71" s="22" t="n">
         <v>350.253</v>
       </c>
       <c r="T71" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S71*0.000000001)^5/(EXP(hP*cL/(S71*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>64597154864578.6</v>
+        <v>64597154864577.4</v>
       </c>
       <c r="U71" s="23" t="n">
         <f aca="false">(S72-S70)/2*0.000000001</f>
@@ -30380,7 +30380,7 @@
       </c>
       <c r="F72" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,42)</f>
-        <v>0.672526269399698</v>
+        <v>0.672526269399687</v>
       </c>
       <c r="G72" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,42)</f>
@@ -30392,7 +30392,7 @@
       </c>
       <c r="I72" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E72+F72))^0.25</f>
-        <v>5458.5670961725</v>
+        <v>5458.56709617249</v>
       </c>
       <c r="J72" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E72+2/3))^0.25</f>
@@ -30400,14 +30400,14 @@
       </c>
       <c r="K72" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I72))-1)</f>
-        <v>19673164336459.7</v>
+        <v>19673164336459.4</v>
       </c>
       <c r="S72" s="22" t="n">
         <v>376.24</v>
       </c>
       <c r="T72" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S72*0.000000001)^5/(EXP(hP*cL/(S72*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>71497913082769.8</v>
+        <v>71497913082768.7</v>
       </c>
       <c r="U72" s="23" t="n">
         <f aca="false">(S73-S71)/2*0.000000001</f>
@@ -30425,7 +30425,7 @@
       </c>
       <c r="F73" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,43)</f>
-        <v>0.677407197757734</v>
+        <v>0.677407197757721</v>
       </c>
       <c r="G73" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,43)</f>
@@ -30437,7 +30437,7 @@
       </c>
       <c r="I73" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E73+F73))^0.25</f>
-        <v>5544.01507401578</v>
+        <v>5544.01507401576</v>
       </c>
       <c r="J73" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E73+2/3))^0.25</f>
@@ -30445,14 +30445,14 @@
       </c>
       <c r="K73" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I73))-1)</f>
-        <v>21347662801045.2</v>
+        <v>21347662801044.9</v>
       </c>
       <c r="S73" s="22" t="n">
         <v>404.156</v>
       </c>
       <c r="T73" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S73*0.000000001)^5/(EXP(hP*cL/(S73*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>76952984228087.5</v>
+        <v>76952984228086.3</v>
       </c>
       <c r="U73" s="23" t="n">
         <f aca="false">(S74-S72)/2*0.000000001</f>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="F74" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,44)</f>
-        <v>0.682091104589113</v>
+        <v>0.682091104589101</v>
       </c>
       <c r="G74" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,44)</f>
@@ -30482,7 +30482,7 @@
       </c>
       <c r="I74" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E74+F74))^0.25</f>
-        <v>5637.37597814017</v>
+        <v>5637.37597814016</v>
       </c>
       <c r="J74" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E74+2/3))^0.25</f>
@@ -30490,14 +30490,14 @@
       </c>
       <c r="K74" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I74))-1)</f>
-        <v>23275546521874</v>
+        <v>23275546521873.7</v>
       </c>
       <c r="S74" s="22" t="n">
         <v>434.143</v>
       </c>
       <c r="T74" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S74*0.000000001)^5/(EXP(hP*cL/(S74*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>80668893331997.8</v>
+        <v>80668893331996.6</v>
       </c>
       <c r="U74" s="23" t="n">
         <f aca="false">(S75-S73)/2*0.000000001</f>
@@ -30515,7 +30515,7 @@
       </c>
       <c r="F75" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,45)</f>
-        <v>0.686517700564339</v>
+        <v>0.686517700564326</v>
       </c>
       <c r="G75" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,45)</f>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="I75" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E75+F75))^0.25</f>
-        <v>5739.15278555111</v>
+        <v>5739.15278555109</v>
       </c>
       <c r="J75" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E75+2/3))^0.25</f>
@@ -30535,14 +30535,14 @@
       </c>
       <c r="K75" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I75))-1)</f>
-        <v>25495518159772.9</v>
+        <v>25495518159772.6</v>
       </c>
       <c r="S75" s="22" t="n">
         <v>466.355</v>
       </c>
       <c r="T75" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S75*0.000000001)^5/(EXP(hP*cL/(S75*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>82492442819656.2</v>
+        <v>82492442819655.1</v>
       </c>
       <c r="U75" s="23" t="n">
         <f aca="false">(S76-S74)/2*0.000000001</f>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="F76" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,46)</f>
-        <v>0.690630169934122</v>
+        <v>0.690630169934107</v>
       </c>
       <c r="G76" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,46)</f>
@@ -30572,7 +30572,7 @@
       </c>
       <c r="I76" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E76+F76))^0.25</f>
-        <v>5849.84849637938</v>
+        <v>5849.84849637937</v>
       </c>
       <c r="J76" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E76+2/3))^0.25</f>
@@ -30580,14 +30580,14 @@
       </c>
       <c r="K76" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I76))-1)</f>
-        <v>28051604952468.3</v>
+        <v>28051604952467.9</v>
       </c>
       <c r="S76" s="22" t="n">
         <v>500.957</v>
       </c>
       <c r="T76" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S76*0.000000001)^5/(EXP(hP*cL/(S76*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>82415430805814.3</v>
+        <v>82415430805813.2</v>
       </c>
       <c r="U76" s="23" t="n">
         <f aca="false">(S77-S75)/2*0.000000001</f>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="F77" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,47)</f>
-        <v>0.694378226245563</v>
+        <v>0.694378226245547</v>
       </c>
       <c r="G77" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,47)</f>
@@ -30617,7 +30617,7 @@
       </c>
       <c r="I77" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E77+F77))^0.25</f>
-        <v>5969.96149680783</v>
+        <v>5969.96149680781</v>
       </c>
       <c r="J77" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E77+2/3))^0.25</f>
@@ -30625,14 +30625,14 @@
       </c>
       <c r="K77" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I77))-1)</f>
-        <v>30993589478825.9</v>
+        <v>30993589478825.5</v>
       </c>
       <c r="S77" s="22" t="n">
         <v>538.126</v>
       </c>
       <c r="T77" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S77*0.000000001)^5/(EXP(hP*cL/(S77*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>80561615772911.3</v>
+        <v>80561615772910.4</v>
       </c>
       <c r="U77" s="23" t="n">
         <f aca="false">(S78-S76)/2*0.000000001</f>
@@ -30650,7 +30650,7 @@
       </c>
       <c r="F78" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,48)</f>
-        <v>0.697721290897148</v>
+        <v>0.697721290897131</v>
       </c>
       <c r="G78" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,48)</f>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="I78" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E78+F78))^0.25</f>
-        <v>6099.98060610439</v>
+        <v>6099.98060610437</v>
       </c>
       <c r="J78" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E78+2/3))^0.25</f>
@@ -30670,14 +30670,14 @@
       </c>
       <c r="K78" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I78))-1)</f>
-        <v>34377371907662</v>
+        <v>34377371907661.6</v>
       </c>
       <c r="S78" s="22" t="n">
         <v>578.053</v>
       </c>
       <c r="T78" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S78*0.000000001)^5/(EXP(hP*cL/(S78*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>77159765753436.9</v>
+        <v>77159765753436</v>
       </c>
       <c r="U78" s="23" t="n">
         <f aca="false">(S79-S77)/2*0.000000001</f>
@@ -30695,7 +30695,7 @@
       </c>
       <c r="F79" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,49)</f>
-        <v>0.700631513410051</v>
+        <v>0.700631513410032</v>
       </c>
       <c r="G79" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,49)</f>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="I79" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E79+F79))^0.25</f>
-        <v>6240.37995888259</v>
+        <v>6240.37995888257</v>
       </c>
       <c r="J79" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E79+2/3))^0.25</f>
@@ -30715,14 +30715,14 @@
       </c>
       <c r="K79" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I79))-1)</f>
-        <v>38265230576460.1</v>
+        <v>38265230576459.6</v>
       </c>
       <c r="S79" s="22" t="n">
         <v>620.943</v>
       </c>
       <c r="T79" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S79*0.000000001)^5/(EXP(hP*cL/(S79*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>72509074323317.1</v>
+        <v>72509074323316.3</v>
       </c>
       <c r="U79" s="23" t="n">
         <f aca="false">(S80-S78)/2*0.000000001</f>
@@ -30740,7 +30740,7 @@
       </c>
       <c r="F80" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,50)</f>
-        <v>0.703096275551466</v>
+        <v>0.703096275551445</v>
       </c>
       <c r="G80" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,50)</f>
@@ -30752,7 +30752,7 @@
       </c>
       <c r="I80" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E80+F80))^0.25</f>
-        <v>6391.61394662092</v>
+        <v>6391.6139466209</v>
       </c>
       <c r="J80" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E80+2/3))^0.25</f>
@@ -30760,14 +30760,14 @@
       </c>
       <c r="K80" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I80))-1)</f>
-        <v>42725947576416.7</v>
+        <v>42725947576416.1</v>
       </c>
       <c r="S80" s="22" t="n">
         <v>667.015</v>
       </c>
       <c r="T80" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S80*0.000000001)^5/(EXP(hP*cL/(S80*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>66943117635368.8</v>
+        <v>66943117635368.1</v>
       </c>
       <c r="U80" s="23" t="n">
         <f aca="false">(S81-S79)/2*0.000000001</f>
@@ -30785,7 +30785,7 @@
       </c>
       <c r="F81" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,51)</f>
-        <v>0.705119775755431</v>
+        <v>0.705119775755408</v>
       </c>
       <c r="G81" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,51)</f>
@@ -30797,7 +30797,7 @@
       </c>
       <c r="I81" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E81+F81))^0.25</f>
-        <v>6554.11252291001</v>
+        <v>6554.11252290999</v>
       </c>
       <c r="J81" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E81+2/3))^0.25</f>
@@ -30805,14 +30805,14 @@
       </c>
       <c r="K81" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I81))-1)</f>
-        <v>47834770096915.2</v>
+        <v>47834770096914.7</v>
       </c>
       <c r="S81" s="22" t="n">
         <v>716.505</v>
       </c>
       <c r="T81" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S81*0.000000001)^5/(EXP(hP*cL/(S81*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>60796768202383.2</v>
+        <v>60796768202382.6</v>
       </c>
       <c r="U81" s="23" t="n">
         <f aca="false">(S82-S80)/2*0.000000001</f>
@@ -30830,7 +30830,7 @@
       </c>
       <c r="F82" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,52)</f>
-        <v>0.706723303297694</v>
+        <v>0.706723303297668</v>
       </c>
       <c r="G82" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,52)</f>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="I82" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E82+F82))^0.25</f>
-        <v>6728.27725235617</v>
+        <v>6728.27725235615</v>
       </c>
       <c r="J82" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E82+2/3))^0.25</f>
@@ -30850,14 +30850,14 @@
       </c>
       <c r="K82" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I82))-1)</f>
-        <v>53673187574689.9</v>
+        <v>53673187574689.3</v>
       </c>
       <c r="S82" s="22" t="n">
         <v>769.667</v>
       </c>
       <c r="T82" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S82*0.000000001)^5/(EXP(hP*cL/(S82*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>54379985124458.8</v>
+        <v>54379985124458.3</v>
       </c>
       <c r="U82" s="23" t="n">
         <f aca="false">(S83-S81)/2*0.000000001</f>
@@ -30875,7 +30875,7 @@
       </c>
       <c r="F83" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,53)</f>
-        <v>0.707943910841903</v>
+        <v>0.707943910841873</v>
       </c>
       <c r="G83" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,53)</f>
@@ -30887,7 +30887,7 @@
       </c>
       <c r="I83" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E83+F83))^0.25</f>
-        <v>6914.47853431871</v>
+        <v>6914.47853431869</v>
       </c>
       <c r="J83" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E83+2/3))^0.25</f>
@@ -30895,14 +30895,14 @@
       </c>
       <c r="K83" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I83))-1)</f>
-        <v>60328519380031.6</v>
+        <v>60328519380030.9</v>
       </c>
       <c r="S83" s="22" t="n">
         <v>826.774</v>
       </c>
       <c r="T83" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S83*0.000000001)^5/(EXP(hP*cL/(S83*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>47959889115818</v>
+        <v>47959889115817.6</v>
       </c>
       <c r="U83" s="23" t="n">
         <f aca="false">(S84-S82)/2*0.000000001</f>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="F84" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,54)</f>
-        <v>0.708831395746813</v>
+        <v>0.70883139574678</v>
       </c>
       <c r="G84" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,54)</f>
@@ -30932,7 +30932,7 @@
       </c>
       <c r="I84" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E84+F84))^0.25</f>
-        <v>7113.05443536212</v>
+        <v>7113.0544353621</v>
       </c>
       <c r="J84" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E84+2/3))^0.25</f>
@@ -30940,14 +30940,14 @@
       </c>
       <c r="K84" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I84))-1)</f>
-        <v>67893326747644.4</v>
+        <v>67893326747643.7</v>
       </c>
       <c r="S84" s="22" t="n">
         <v>888.117</v>
       </c>
       <c r="T84" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S84*0.000000001)^5/(EXP(hP*cL/(S84*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>41751236769013.3</v>
+        <v>41751236769013</v>
       </c>
       <c r="U84" s="23" t="n">
         <f aca="false">(S85-S83)/2*0.000000001</f>
@@ -30965,7 +30965,7 @@
       </c>
       <c r="F85" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,55)</f>
-        <v>0.709443795614982</v>
+        <v>0.709443795614946</v>
       </c>
       <c r="G85" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,55)</f>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="I85" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E85+F85))^0.25</f>
-        <v>7324.31149390556</v>
+        <v>7324.31149390554</v>
       </c>
       <c r="J85" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E85+2/3))^0.25</f>
@@ -30985,14 +30985,14 @@
       </c>
       <c r="K85" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I85))-1)</f>
-        <v>76464683213560.1</v>
+        <v>76464683213559.3</v>
       </c>
       <c r="S85" s="22" t="n">
         <v>954.013</v>
       </c>
       <c r="T85" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S85*0.000000001)^5/(EXP(hP*cL/(S85*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>35913071785964.5</v>
+        <v>35913071785964.3</v>
       </c>
       <c r="U85" s="23" t="n">
         <f aca="false">(S86-S84)/2*0.000000001</f>
@@ -31010,7 +31010,7 @@
       </c>
       <c r="F86" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,56)</f>
-        <v>0.709841942992282</v>
+        <v>0.70984194299224</v>
       </c>
       <c r="G86" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,56)</f>
@@ -31022,7 +31022,7 @@
       </c>
       <c r="I86" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E86+F86))^0.25</f>
-        <v>7548.52770096623</v>
+        <v>7548.52770096621</v>
       </c>
       <c r="J86" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E86+2/3))^0.25</f>
@@ -31030,14 +31030,14 @@
       </c>
       <c r="K86" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I86))-1)</f>
-        <v>86143355784333.5</v>
+        <v>86143355784332.7</v>
       </c>
       <c r="S86" s="22" t="n">
         <v>1024.797</v>
       </c>
       <c r="T86" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S86*0.000000001)^5/(EXP(hP*cL/(S86*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>30552404043955.5</v>
+        <v>30552404043955.3</v>
       </c>
       <c r="U86" s="23" t="n">
         <f aca="false">(S87-S85)/2*0.000000001</f>
@@ -31055,7 +31055,7 @@
       </c>
       <c r="F87" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,57)</f>
-        <v>0.710083297814694</v>
+        <v>0.710083297814647</v>
       </c>
       <c r="G87" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,57)</f>
@@ -31067,7 +31067,7 @@
       </c>
       <c r="I87" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E87+F87))^0.25</f>
-        <v>7785.95734347338</v>
+        <v>7785.95734347336</v>
       </c>
       <c r="J87" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E87+2/3))^0.25</f>
@@ -31075,14 +31075,14 @@
       </c>
       <c r="K87" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I87))-1)</f>
-        <v>97032946809563.9</v>
+        <v>97032946809562.9</v>
       </c>
       <c r="S87" s="22" t="n">
         <v>1100.834</v>
       </c>
       <c r="T87" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S87*0.000000001)^5/(EXP(hP*cL/(S87*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>25729605406477.8</v>
+        <v>25729605406477.6</v>
       </c>
       <c r="U87" s="23" t="n">
         <f aca="false">(S88-S86)/2*0.000000001</f>
@@ -31100,7 +31100,7 @@
       </c>
       <c r="F88" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,58)</f>
-        <v>0.710219381497255</v>
+        <v>0.710219381497201</v>
       </c>
       <c r="G88" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,58)</f>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="I88" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E88+F88))^0.25</f>
-        <v>8036.83889292048</v>
+        <v>8036.83889292046</v>
       </c>
       <c r="J88" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E88+2/3))^0.25</f>
@@ -31120,14 +31120,14 @@
       </c>
       <c r="K88" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I88))-1)</f>
-        <v>109239129618654</v>
+        <v>109239129618653</v>
       </c>
       <c r="S88" s="22" t="n">
         <v>1182.512</v>
       </c>
       <c r="T88" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S88*0.000000001)^5/(EXP(hP*cL/(S88*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>21467325468405.1</v>
+        <v>21467325468404.9</v>
       </c>
       <c r="U88" s="23" t="n">
         <f aca="false">(S89-S87)/2*0.000000001</f>
@@ -31145,7 +31145,7 @@
       </c>
       <c r="F89" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,59)</f>
-        <v>0.710290544777671</v>
+        <v>0.710290544777609</v>
       </c>
       <c r="G89" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,59)</f>
@@ -31157,7 +31157,7 @@
       </c>
       <c r="I89" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E89+F89))^0.25</f>
-        <v>8301.40198687696</v>
+        <v>8301.40198687694</v>
       </c>
       <c r="J89" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E89+2/3))^0.25</f>
@@ -31165,14 +31165,14 @@
       </c>
       <c r="K89" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I89))-1)</f>
-        <v>122868876252179</v>
+        <v>122868876252178</v>
       </c>
       <c r="S89" s="22" t="n">
         <v>1270.25</v>
       </c>
       <c r="T89" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S89*0.000000001)^5/(EXP(hP*cL/(S89*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>17758803409792.2</v>
+        <v>17758803409792.1</v>
       </c>
       <c r="U89" s="23" t="n">
         <f aca="false">(S90-S88)/2*0.000000001</f>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="F90" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,60)</f>
-        <v>0.710325323319857</v>
+        <v>0.710325323319787</v>
       </c>
       <c r="G90" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,60)</f>
@@ -31202,7 +31202,7 @@
       </c>
       <c r="I90" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E90+F90))^0.25</f>
-        <v>8579.87612203612</v>
+        <v>8579.8761220361</v>
       </c>
       <c r="J90" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E90+2/3))^0.25</f>
@@ -31210,14 +31210,14 @@
       </c>
       <c r="K90" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I90))-1)</f>
-        <v>138029855631777</v>
+        <v>138029855631775</v>
       </c>
       <c r="S90" s="22" t="n">
         <v>1364.499</v>
       </c>
       <c r="T90" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S90*0.000000001)^5/(EXP(hP*cL/(S90*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>14576329483703.9</v>
+        <v>14576329483703.8</v>
       </c>
       <c r="U90" s="23" t="n">
         <f aca="false">(S91-S89)/2*0.000000001</f>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="F91" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,61)</f>
-        <v>0.710342036594481</v>
+        <v>0.710342036594401</v>
       </c>
       <c r="G91" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,61)</f>
@@ -31247,7 +31247,7 @@
       </c>
       <c r="I91" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E91+F91))^0.25</f>
-        <v>8872.49890159568</v>
+        <v>8872.49890159566</v>
       </c>
       <c r="J91" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E91+2/3))^0.25</f>
@@ -31255,14 +31255,14 @@
       </c>
       <c r="K91" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I91))-1)</f>
-        <v>154829956074378</v>
+        <v>154829956074377</v>
       </c>
       <c r="S91" s="22" t="n">
         <v>1465.74</v>
       </c>
       <c r="T91" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S91*0.000000001)^5/(EXP(hP*cL/(S91*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>11878676861475.4</v>
+        <v>11878676861475.3</v>
       </c>
       <c r="U91" s="23" t="n">
         <f aca="false">(S92-S90)/2*0.000000001</f>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="F92" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,62)</f>
-        <v>0.710351105053317</v>
+        <v>0.710351105053224</v>
       </c>
       <c r="G92" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,62)</f>
@@ -31292,7 +31292,7 @@
       </c>
       <c r="I92" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E92+F92))^0.25</f>
-        <v>9179.52291123178</v>
+        <v>9179.52291123175</v>
       </c>
       <c r="J92" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E92+2/3))^0.25</f>
@@ -31300,14 +31300,14 @@
       </c>
       <c r="K92" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I92))-1)</f>
-        <v>173376904303325</v>
+        <v>173376904303323</v>
       </c>
       <c r="S92" s="22" t="n">
         <v>1574.493</v>
       </c>
       <c r="T92" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S92*0.000000001)^5/(EXP(hP*cL/(S92*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>9616882348947.4</v>
+        <v>9616882348947.35</v>
       </c>
       <c r="U92" s="23" t="n">
         <f aca="false">(S93-S91)/2*0.000000001</f>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="F93" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,63)</f>
-        <v>0.710357723165527</v>
+        <v>0.710357723165425</v>
       </c>
       <c r="G93" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,63)</f>
@@ -31337,7 +31337,7 @@
       </c>
       <c r="I93" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E93+F93))^0.25</f>
-        <v>9501.22114553663</v>
+        <v>9501.2211455366</v>
       </c>
       <c r="J93" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E93+2/3))^0.25</f>
@@ -31345,14 +31345,14 @@
       </c>
       <c r="K93" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I93))-1)</f>
-        <v>193777975049445</v>
+        <v>193777975049444</v>
       </c>
       <c r="S93" s="22" t="n">
         <v>1691.315</v>
       </c>
       <c r="T93" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S93*0.000000001)^5/(EXP(hP*cL/(S93*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>7739049298030.6</v>
+        <v>7739049298030.56</v>
       </c>
       <c r="U93" s="23" t="n">
         <f aca="false">(S94-S92)/2*0.000000001</f>
@@ -31370,7 +31370,7 @@
       </c>
       <c r="F94" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,64)</f>
-        <v>0.710364153365868</v>
+        <v>0.71036415336576</v>
       </c>
       <c r="G94" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,64)</f>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="I94" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E94+F94))^0.25</f>
-        <v>9837.89098449824</v>
+        <v>9837.89098449822</v>
       </c>
       <c r="J94" s="20" t="n">
         <f aca="false">$B$6*(0.75*(E94+2/3))^0.25</f>
@@ -31390,14 +31390,14 @@
       </c>
       <c r="K94" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I94))-1)</f>
-        <v>216139777811901</v>
+        <v>216139777811900</v>
       </c>
       <c r="S94" s="22" t="n">
         <v>1816.805</v>
       </c>
       <c r="T94" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S94*0.000000001)^5/(EXP(hP*cL/(S94*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>6193669889095.34</v>
+        <v>6193669889095.31</v>
       </c>
       <c r="U94" s="23" t="n">
         <f aca="false">(S95-S93)/2*0.000000001</f>
@@ -31415,7 +31415,7 @@
       </c>
       <c r="F95" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,65)</f>
-        <v>0.710371287349067</v>
+        <v>0.710371287348953</v>
       </c>
       <c r="G95" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,65)</f>
@@ -31435,14 +31435,14 @@
       </c>
       <c r="K95" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I95))-1)</f>
-        <v>240568114868469</v>
+        <v>240568114868467</v>
       </c>
       <c r="S95" s="22" t="n">
         <v>1951.605</v>
       </c>
       <c r="T95" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S95*0.000000001)^5/(EXP(hP*cL/(S95*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4931942606475.08</v>
+        <v>4931942606475.06</v>
       </c>
       <c r="U95" s="23" t="n">
         <f aca="false">(S96-S94)/2*0.000000001</f>
@@ -31460,7 +31460,7 @@
       </c>
       <c r="F96" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,66)</f>
-        <v>0.710379500225859</v>
+        <v>0.71037950022576</v>
       </c>
       <c r="G96" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,66)</f>
@@ -31480,14 +31480,14 @@
       </c>
       <c r="K96" s="23" t="n">
         <f aca="false">2*hP*cL^2/($B$7*0.000000001)^5/(EXP(hP*cL/($B$7*0.000000001*kB*I96))-1)</f>
-        <v>267167909921976</v>
+        <v>267167909921975</v>
       </c>
       <c r="S96" s="22" t="n">
         <v>2096.408</v>
       </c>
       <c r="T96" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S96*0.000000001)^5/(EXP(hP*cL/(S96*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3909130301667.26</v>
+        <v>3909130301667.24</v>
       </c>
       <c r="U96" s="23" t="n">
         <f aca="false">(S97-S95)/2*0.000000001</f>
@@ -31505,7 +31505,7 @@
       </c>
       <c r="F97" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,67)</f>
-        <v>0.710389024882073</v>
+        <v>0.710389024882015</v>
       </c>
       <c r="G97" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,67)</f>
@@ -31532,7 +31532,7 @@
       </c>
       <c r="T97" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S97*0.000000001)^5/(EXP(hP*cL/(S97*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3085348152298.03</v>
+        <v>3085348152298.02</v>
       </c>
       <c r="U97" s="23" t="n">
         <f aca="false">(S98-S96)/2*0.000000001</f>
@@ -31550,7 +31550,7 @@
       </c>
       <c r="F98" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,68)</f>
-        <v>0.710400082935264</v>
+        <v>0.710400082935245</v>
       </c>
       <c r="G98" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,68)</f>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="T98" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S98*0.000000001)^5/(EXP(hP*cL/(S98*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>2425729943745.37</v>
+        <v>2425729943745.36</v>
       </c>
       <c r="U98" s="23" t="n">
         <f aca="false">(S99-S97)/2*0.000000001</f>
@@ -31595,7 +31595,7 @@
       </c>
       <c r="F99" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,69)</f>
-        <v>0.710412922809111</v>
+        <v>0.710412922809113</v>
       </c>
       <c r="G99" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,69)</f>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="T99" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S99*0.000000001)^5/(EXP(hP*cL/(S99*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1900362666610.99</v>
+        <v>1900362666610.98</v>
       </c>
       <c r="U99" s="23" t="n">
         <f aca="false">(S100-S98)/2*0.000000001</f>
@@ -31640,7 +31640,7 @@
       </c>
       <c r="F100" s="17" t="n">
         <f aca="false">INDEX(Data!$B$4:$B$74,70)</f>
-        <v>0.710427832914435</v>
+        <v>0.710427832914446</v>
       </c>
       <c r="G100" s="31" t="n">
         <f aca="false">INDEX(Data!$C$4:$C$74,70)</f>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="T100" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S100*0.000000001)^5/(EXP(hP*cL/(S100*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1483927915125.46</v>
+        <v>1483927915125.45</v>
       </c>
       <c r="U100" s="23" t="n">
         <f aca="false">(S101-S99)/2*0.000000001</f>
@@ -31729,7 +31729,7 @@
       </c>
       <c r="T102" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S102*0.000000001)^5/(EXP(hP*cL/(S102*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>896953645441.247</v>
+        <v>896953645441.244</v>
       </c>
       <c r="U102" s="23" t="n">
         <f aca="false">(S103-S101)/2*0.000000001</f>
@@ -31746,7 +31746,7 @@
       </c>
       <c r="T103" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S103*0.000000001)^5/(EXP(hP*cL/(S103*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>694630930880.14</v>
+        <v>694630930880.138</v>
       </c>
       <c r="U103" s="23" t="n">
         <f aca="false">(S104-S102)/2*0.000000001</f>
@@ -31763,7 +31763,7 @@
       </c>
       <c r="T104" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S104*0.000000001)^5/(EXP(hP*cL/(S104*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>536697945149.734</v>
+        <v>536697945149.732</v>
       </c>
       <c r="U104" s="23" t="n">
         <f aca="false">(S105-S103)/2*0.000000001</f>
@@ -31780,7 +31780,7 @@
       </c>
       <c r="T105" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S105*0.000000001)^5/(EXP(hP*cL/(S105*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>413788286443.935</v>
+        <v>413788286443.933</v>
       </c>
       <c r="U105" s="23" t="n">
         <f aca="false">(S106-S104)/2*0.000000001</f>
@@ -31797,7 +31797,7 @@
       </c>
       <c r="T106" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S106*0.000000001)^5/(EXP(hP*cL/(S106*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>318399641040.646</v>
+        <v>318399641040.645</v>
       </c>
       <c r="U106" s="23" t="n">
         <f aca="false">(S107-S105)/2*0.000000001</f>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="T107" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S107*0.000000001)^5/(EXP(hP*cL/(S107*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>244557574908.843</v>
+        <v>244557574908.842</v>
       </c>
       <c r="U107" s="23" t="n">
         <f aca="false">(S108-S106)/2*0.000000001</f>
@@ -31831,7 +31831,7 @@
       </c>
       <c r="T108" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S108*0.000000001)^5/(EXP(hP*cL/(S108*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>187527631470.364</v>
+        <v>187527631470.363</v>
       </c>
       <c r="U108" s="23" t="n">
         <f aca="false">(S109-S107)/2*0.000000001</f>
@@ -31865,7 +31865,7 @@
       </c>
       <c r="T110" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S110*0.000000001)^5/(EXP(hP*cL/(S110*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>109769956502.379</v>
+        <v>109769956502.378</v>
       </c>
       <c r="U110" s="23" t="n">
         <f aca="false">(S111-S109)/2*0.000000001</f>
@@ -31882,7 +31882,7 @@
       </c>
       <c r="T111" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S111*0.000000001)^5/(EXP(hP*cL/(S111*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>83814025702.9698</v>
+        <v>83814025702.9695</v>
       </c>
       <c r="U111" s="23" t="n">
         <f aca="false">(S112-S110)/2*0.000000001</f>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="T112" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S112*0.000000001)^5/(EXP(hP*cL/(S112*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>63918352884.489</v>
+        <v>63918352884.4888</v>
       </c>
       <c r="U112" s="23" t="n">
         <f aca="false">(S113-S111)/2*0.000000001</f>
@@ -31916,7 +31916,7 @@
       </c>
       <c r="T113" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S113*0.000000001)^5/(EXP(hP*cL/(S113*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>48691148028.7492</v>
+        <v>48691148028.7491</v>
       </c>
       <c r="U113" s="23" t="n">
         <f aca="false">(S114-S112)/2*0.000000001</f>
@@ -31933,7 +31933,7 @@
       </c>
       <c r="T114" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S114*0.000000001)^5/(EXP(hP*cL/(S114*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>37053302793.9214</v>
+        <v>37053302793.9213</v>
       </c>
       <c r="U114" s="23" t="n">
         <f aca="false">(S115-S113)/2*0.000000001</f>
@@ -31950,7 +31950,7 @@
       </c>
       <c r="T115" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S115*0.000000001)^5/(EXP(hP*cL/(S115*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>28170203708.4607</v>
+        <v>28170203708.4606</v>
       </c>
       <c r="U115" s="23" t="n">
         <f aca="false">(S116-S114)/2*0.000000001</f>
@@ -31967,7 +31967,7 @@
       </c>
       <c r="T116" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S116*0.000000001)^5/(EXP(hP*cL/(S116*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>21397868960.9361</v>
+        <v>21397868960.936</v>
       </c>
       <c r="U116" s="23" t="n">
         <f aca="false">(S117-S115)/2*0.000000001</f>
@@ -32018,7 +32018,7 @@
       </c>
       <c r="T119" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S119*0.000000001)^5/(EXP(hP*cL/(S119*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>9334510403.98083</v>
+        <v>9334510403.98081</v>
       </c>
       <c r="U119" s="23" t="n">
         <f aca="false">(S120-S118)/2*0.000000001</f>
@@ -32035,7 +32035,7 @@
       </c>
       <c r="T120" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S120*0.000000001)^5/(EXP(hP*cL/(S120*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>7069784053.138</v>
+        <v>7069784053.13798</v>
       </c>
       <c r="U120" s="23" t="n">
         <f aca="false">(S121-S119)/2*0.000000001</f>
@@ -32052,7 +32052,7 @@
       </c>
       <c r="T121" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S121*0.000000001)^5/(EXP(hP*cL/(S121*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>5351315428.27379</v>
+        <v>5351315428.27377</v>
       </c>
       <c r="U121" s="23" t="n">
         <f aca="false">(S122-S120)/2*0.000000001</f>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="T122" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S122*0.000000001)^5/(EXP(hP*cL/(S122*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4048307714.306</v>
+        <v>4048307714.30599</v>
       </c>
       <c r="U122" s="23" t="n">
         <f aca="false">(S123-S121)/2*0.000000001</f>
@@ -32086,7 +32086,7 @@
       </c>
       <c r="T123" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S123*0.000000001)^5/(EXP(hP*cL/(S123*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3060997412.88598</v>
+        <v>3060997412.88597</v>
       </c>
       <c r="U123" s="23" t="n">
         <f aca="false">(S124-S122)/2*0.000000001</f>
@@ -32154,7 +32154,7 @@
       </c>
       <c r="T127" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S127*0.000000001)^5/(EXP(hP*cL/(S127*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>996074758.77383</v>
+        <v>996074758.773827</v>
       </c>
       <c r="U127" s="23" t="n">
         <f aca="false">(S128-S126)/2*0.000000001</f>
@@ -32171,7 +32171,7 @@
       </c>
       <c r="T128" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S128*0.000000001)^5/(EXP(hP*cL/(S128*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>751595209.215927</v>
+        <v>751595209.215925</v>
       </c>
       <c r="U128" s="23" t="n">
         <f aca="false">(S129-S127)/2*0.000000001</f>
@@ -32188,7 +32188,7 @@
       </c>
       <c r="T129" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S129*0.000000001)^5/(EXP(hP*cL/(S129*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>566935176.452276</v>
+        <v>566935176.452274</v>
       </c>
       <c r="U129" s="23" t="n">
         <f aca="false">(S130-S128)/2*0.000000001</f>
@@ -32205,7 +32205,7 @@
       </c>
       <c r="T130" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S130*0.000000001)^5/(EXP(hP*cL/(S130*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>427514041.470436</v>
+        <v>427514041.470435</v>
       </c>
       <c r="U130" s="23" t="n">
         <f aca="false">(S131-S129)/2*0.000000001</f>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="T131" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S131*0.000000001)^5/(EXP(hP*cL/(S131*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>322288177.202813</v>
+        <v>322288177.202812</v>
       </c>
       <c r="U131" s="23" t="n">
         <f aca="false">(S132-S130)/2*0.000000001</f>
@@ -32239,7 +32239,7 @@
       </c>
       <c r="T132" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S132*0.000000001)^5/(EXP(hP*cL/(S132*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>242898123.41893</v>
+        <v>242898123.418929</v>
       </c>
       <c r="U132" s="23" t="n">
         <f aca="false">(S133-S131)/2*0.000000001</f>
@@ -32290,7 +32290,7 @@
       </c>
       <c r="T135" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S135*0.000000001)^5/(EXP(hP*cL/(S135*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>103837980.487707</v>
+        <v>103837980.487706</v>
       </c>
       <c r="U135" s="23" t="n">
         <f aca="false">(S136-S134)/2*0.000000001</f>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="T136" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S136*0.000000001)^5/(EXP(hP*cL/(S136*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>78190599.876553</v>
+        <v>78190599.8765527</v>
       </c>
       <c r="U136" s="23" t="n">
         <f aca="false">(S137-S135)/2*0.000000001</f>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="T137" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S137*0.000000001)^5/(EXP(hP*cL/(S137*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>58867242.3936558</v>
+        <v>58867242.3936556</v>
       </c>
       <c r="U137" s="23" t="n">
         <f aca="false">(S138-S136)/2*0.000000001</f>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="T138" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S138*0.000000001)^5/(EXP(hP*cL/(S138*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>44311791.9208009</v>
+        <v>44311791.9208008</v>
       </c>
       <c r="U138" s="23" t="n">
         <f aca="false">(S139-S137)/2*0.000000001</f>
@@ -32375,7 +32375,7 @@
       </c>
       <c r="T140" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S140*0.000000001)^5/(EXP(hP*cL/(S140*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>25096330.9771608</v>
+        <v>25096330.9771607</v>
       </c>
       <c r="U140" s="23" t="n">
         <f aca="false">(S141-S139)/2*0.000000001</f>
@@ -32392,7 +32392,7 @@
       </c>
       <c r="T141" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S141*0.000000001)^5/(EXP(hP*cL/(S141*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>18882732.0912649</v>
+        <v>18882732.0912648</v>
       </c>
       <c r="U141" s="23" t="n">
         <f aca="false">(S142-S140)/2*0.000000001</f>
@@ -32409,7 +32409,7 @@
       </c>
       <c r="T142" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S142*0.000000001)^5/(EXP(hP*cL/(S142*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>14205759.2690719</v>
+        <v>14205759.2690718</v>
       </c>
       <c r="U142" s="23" t="n">
         <f aca="false">(S143-S141)/2*0.000000001</f>
@@ -32443,7 +32443,7 @@
       </c>
       <c r="T144" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S144*0.000000001)^5/(EXP(hP*cL/(S144*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>8037369.74154944</v>
+        <v>8037369.74154942</v>
       </c>
       <c r="U144" s="23" t="n">
         <f aca="false">(S145-S143)/2*0.000000001</f>
@@ -32460,7 +32460,7 @@
       </c>
       <c r="T145" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S145*0.000000001)^5/(EXP(hP*cL/(S145*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>6044644.16583729</v>
+        <v>6044644.16583728</v>
       </c>
       <c r="U145" s="23" t="n">
         <f aca="false">(S146-S144)/2*0.000000001</f>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="T146" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S146*0.000000001)^5/(EXP(hP*cL/(S146*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>4545549.62170543</v>
+        <v>4545549.62170542</v>
       </c>
       <c r="U146" s="23" t="n">
         <f aca="false">(S147-S145)/2*0.000000001</f>
@@ -32494,7 +32494,7 @@
       </c>
       <c r="T147" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S147*0.000000001)^5/(EXP(hP*cL/(S147*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>3417935.22047005</v>
+        <v>3417935.22047004</v>
       </c>
       <c r="U147" s="23" t="n">
         <f aca="false">(S148-S146)/2*0.000000001</f>
@@ -32511,7 +32511,7 @@
       </c>
       <c r="T148" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S148*0.000000001)^5/(EXP(hP*cL/(S148*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>2569837.53071657</v>
+        <v>2569837.53071656</v>
       </c>
       <c r="U148" s="23" t="n">
         <f aca="false">(S149-S147)/2*0.000000001</f>
@@ -32545,7 +32545,7 @@
       </c>
       <c r="T150" s="23" t="n">
         <f aca="false">2*PI()*SUMPRODUCT(2*hP*cL^2/(S150*0.000000001)^5/(EXP(hP*cL/(S150*0.000000001*kB*$I$31:$I$101))-1),$G$31:$G$101,$H$31:$H$101)</f>
-        <v>1452420.50805358</v>
+        <v>1452420.50805357</v>
       </c>
       <c r="U150" s="23" t="n">
         <f aca="false">(S150-S149)/2*0.000000001</f>
@@ -35732,7 +35732,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="33" t="n">
-        <v>0.577319523037564</v>
+        <v>0.577319523037558</v>
       </c>
       <c r="C4" s="32" t="n">
         <v>1</v>
@@ -35761,7 +35761,7 @@
         <v>0.001</v>
       </c>
       <c r="B5" s="33" t="n">
-        <v>0.579055250680859</v>
+        <v>0.579055250680853</v>
       </c>
       <c r="C5" s="32" t="n">
         <v>0.992668960469239</v>
@@ -35779,7 +35779,7 @@
         <v>0.3</v>
       </c>
       <c r="J5" s="17" t="n">
-        <v>0.547702809428829</v>
+        <v>0.547491993284075</v>
       </c>
       <c r="K5" s="17" t="n">
         <v>0.547722557505166</v>
@@ -35790,7 +35790,7 @@
         <v>0.00116114328588683</v>
       </c>
       <c r="B6" s="33" t="n">
-        <v>0.579285383685983</v>
+        <v>0.579285383685977</v>
       </c>
       <c r="C6" s="32" t="n">
         <v>0.991660999890295</v>
@@ -35808,7 +35808,7 @@
         <v>0.1</v>
       </c>
       <c r="J6" s="17" t="n">
-        <v>0.316139151263278</v>
+        <v>0.315690971659811</v>
       </c>
       <c r="K6" s="17" t="n">
         <v>0.316227766016838</v>
@@ -35819,7 +35819,7 @@
         <v>0.00134825373036006</v>
       </c>
       <c r="B7" s="33" t="n">
-        <v>0.579544691018356</v>
+        <v>0.57954469101835</v>
       </c>
       <c r="C7" s="32" t="n">
         <v>0.990518535926439</v>
@@ -35837,7 +35837,7 @@
         <v>0.03</v>
       </c>
       <c r="J7" s="17" t="n">
-        <v>0.172943478100771</v>
+        <v>0.172583739359305</v>
       </c>
       <c r="K7" s="17" t="n">
         <v>0.173205080756888</v>
@@ -35848,7 +35848,7 @@
         <v>0.00156551576667946</v>
       </c>
       <c r="B8" s="33" t="n">
-        <v>0.579836621494636</v>
+        <v>0.57983662149463</v>
       </c>
       <c r="C8" s="32" t="n">
         <v>0.989224387726524</v>
@@ -35866,7 +35866,7 @@
         <v>0.01</v>
       </c>
       <c r="J8" s="17" t="n">
-        <v>0.0994367714391393</v>
+        <v>0.0994862075950151</v>
       </c>
       <c r="K8" s="17" t="n">
         <v>0.1</v>
@@ -35877,7 +35877,7 @@
         <v>0.00181778812142982</v>
       </c>
       <c r="B9" s="33" t="n">
-        <v>0.580164984214312</v>
+        <v>0.580164984214306</v>
       </c>
       <c r="C9" s="32" t="n">
         <v>0.987759327833826</v>
@@ -35895,7 +35895,7 @@
         <v>0.003</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.0536619392158208</v>
+        <v>0.05442355569183</v>
       </c>
       <c r="K9" s="17" t="n">
         <v>0.0547722557505166</v>
@@ -35906,7 +35906,7 @@
         <v>0.00211071247236307</v>
       </c>
       <c r="B10" s="33" t="n">
-        <v>0.580533976909004</v>
+        <v>0.580533976908998</v>
       </c>
       <c r="C10" s="32" t="n">
         <v>0.986101867993547</v>
@@ -35924,7 +35924,7 @@
         <v>0.001</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.0298475745017908</v>
+        <v>0.0313986116286755</v>
       </c>
       <c r="K10" s="17" t="n">
         <v>0.0316227766016838</v>
@@ -35935,7 +35935,7 @@
         <v>0.00245083961572197</v>
       </c>
       <c r="B11" s="33" t="n">
-        <v>0.580948214567638</v>
+        <v>0.580948214567632</v>
       </c>
       <c r="C11" s="32" t="n">
         <v>0.984228028817382</v>
@@ -35955,7 +35955,7 @@
         <v>0.00284577596458102</v>
       </c>
       <c r="B12" s="33" t="n">
-        <v>0.581412757823075</v>
+        <v>0.581412757823069</v>
       </c>
       <c r="C12" s="32" t="n">
         <v>0.982111093575599</v>
@@ -35975,7 +35975,7 @@
         <v>0.00330435365441136</v>
       </c>
       <c r="B13" s="33" t="n">
-        <v>0.581933140447196</v>
+        <v>0.58193314044719</v>
       </c>
       <c r="C13" s="32" t="n">
         <v>0.979721346862627</v>
@@ -35995,7 +35995,7 @@
         <v>0.00383682806001536</v>
       </c>
       <c r="B14" s="33" t="n">
-        <v>0.582515395139863</v>
+        <v>0.582515395139857</v>
       </c>
       <c r="C14" s="32" t="n">
         <v>0.977025799493334</v>
@@ -36015,7 +36015,7 @@
         <v>0.00445510714098902</v>
       </c>
       <c r="B15" s="33" t="n">
-        <v>0.583166076610894</v>
+        <v>0.583166076610888</v>
       </c>
       <c r="C15" s="32" t="n">
         <v>0.973987901761685</v>
@@ -36035,7 +36035,7 @@
         <v>0.00517301774466587</v>
       </c>
       <c r="B16" s="33" t="n">
-        <v>0.583892151149632</v>
+        <v>0.583892151149625</v>
       </c>
       <c r="C16" s="32" t="n">
         <v>0.970567248163202</v>
@@ -36055,7 +36055,7 @@
         <v>0.00600661482199219</v>
       </c>
       <c r="B17" s="33" t="n">
-        <v>0.584701246853153</v>
+        <v>0.584701246853147</v>
       </c>
       <c r="C17" s="32" t="n">
         <v>0.966719277883874</v>
@@ -36075,7 +36075,7 @@
         <v>0.00697454047146454</v>
       </c>
       <c r="B18" s="33" t="n">
-        <v>0.585601646526454</v>
+        <v>0.585601646526448</v>
       </c>
       <c r="C18" s="32" t="n">
         <v>0.962394976831515</v>
@@ -36095,7 +36095,7 @@
         <v>0.00809844084058701</v>
       </c>
       <c r="B19" s="33" t="n">
-        <v>0.586602104365434</v>
+        <v>0.586602104365428</v>
       </c>
       <c r="C19" s="32" t="n">
         <v>0.957540588775986</v>
@@ -36115,7 +36115,7 @@
         <v>0.00940345020819929</v>
       </c>
       <c r="B20" s="33" t="n">
-        <v>0.58771191687879</v>
+        <v>0.587711916878784</v>
       </c>
       <c r="C20" s="32" t="n">
         <v>0.95209734532043</v>
@@ -36135,7 +36135,7 @@
         <v>0.0109187530734217</v>
       </c>
       <c r="B21" s="33" t="n">
-        <v>0.58894089452217</v>
+        <v>0.588940894522163</v>
       </c>
       <c r="C21" s="32" t="n">
         <v>0.946001226997373</v>
@@ -36155,7 +36155,7 @@
         <v>0.0126782368214598</v>
       </c>
       <c r="B22" s="33" t="n">
-        <v>0.590299316202863</v>
+        <v>0.590299316202856</v>
       </c>
       <c r="C22" s="32" t="n">
         <v>0.939182770821766</v>
@@ -36175,7 +36175,7 @@
         <v>0.0147212495621212</v>
       </c>
       <c r="B23" s="33" t="n">
-        <v>0.591797863318852</v>
+        <v>0.591797863318846</v>
       </c>
       <c r="C23" s="32" t="n">
         <v>0.931566943185061</v>
@@ -36195,7 +36195,7 @@
         <v>0.0170934800889215</v>
       </c>
       <c r="B24" s="33" t="n">
-        <v>0.59344752968076</v>
+        <v>0.593447529680754</v>
       </c>
       <c r="C24" s="32" t="n">
         <v>0.923073101078901</v>
@@ -36215,7 +36215,7 @@
         <v>0.0198479796376913</v>
       </c>
       <c r="B25" s="33" t="n">
-        <v>0.595259503394157</v>
+        <v>0.595259503394151</v>
       </c>
       <c r="C25" s="32" t="n">
         <v>0.913615069316814</v>
@@ -36226,7 +36226,7 @@
         <v>0.0230463482947238</v>
       </c>
       <c r="B26" s="33" t="n">
-        <v>0.597245016583342</v>
+        <v>0.597245016583336</v>
       </c>
       <c r="C26" s="32" t="n">
         <v>0.903101366673764</v>
@@ -36237,7 +36237,7 @@
         <v>0.0267601125866279</v>
       </c>
       <c r="B27" s="33" t="n">
-        <v>0.599415158755064</v>
+        <v>0.599415158755058</v>
       </c>
       <c r="C27" s="32" t="n">
         <v>0.891435619641988</v>
@@ -36248,7 +36248,7 @@
         <v>0.0310723250595386</v>
       </c>
       <c r="B28" s="33" t="n">
-        <v>0.601780649680794</v>
+        <v>0.601780649680787</v>
       </c>
       <c r="C28" s="32" t="n">
         <v>0.878517208702097</v>
@@ -36259,7 +36259,7 @@
         <v>0.0360794216197763</v>
       </c>
       <c r="B29" s="33" t="n">
-        <v>0.604351567979417</v>
+        <v>0.604351567979411</v>
       </c>
       <c r="C29" s="32" t="n">
         <v>0.864242198439214</v>
@@ -36270,7 +36270,7 @@
         <v>0.0418933781724833</v>
       </c>
       <c r="B30" s="33" t="n">
-        <v>0.607137032181322</v>
+        <v>0.607137032181315</v>
       </c>
       <c r="C30" s="32" t="n">
         <v>0.848504609182747</v>
@@ -36281,7 +36281,7 @@
         <v>0.0486442147880968</v>
       </c>
       <c r="B31" s="33" t="n">
-        <v>0.610143233826245</v>
+        <v>0.610143233826238</v>
       </c>
       <c r="C31" s="32" t="n">
         <v>0.831198093639455</v>
@@ -36292,7 +36292,7 @@
         <v>0.0564829033984354</v>
       </c>
       <c r="B32" s="33" t="n">
-        <v>0.613377262589377</v>
+        <v>0.61337726258937</v>
       </c>
       <c r="C32" s="32" t="n">
         <v>0.812218086530342</v>
@@ -36303,7 +36303,7 @@
         <v>0.0655847440484876</v>
       </c>
       <c r="B33" s="33" t="n">
-        <v>0.616842988473331</v>
+        <v>0.616842988473324</v>
       </c>
       <c r="C33" s="32" t="n">
         <v>0.791464497559914</v>
@@ -36314,7 +36314,7 @@
         <v>0.0761532852085076</v>
       </c>
       <c r="B34" s="33" t="n">
-        <v>0.62054143628366</v>
+        <v>0.620541436283652</v>
       </c>
       <c r="C34" s="32" t="n">
         <v>0.768845016816333</v>
@@ -36325,7 +36325,7 @@
         <v>0.0884248758180833</v>
       </c>
       <c r="B35" s="33" t="n">
-        <v>0.624470347888569</v>
+        <v>0.624470347888562</v>
       </c>
       <c r="C35" s="32" t="n">
         <v>0.744279095168773</v>
@@ -36336,7 +36336,7 @@
         <v>0.102673950861544</v>
       </c>
       <c r="B36" s="33" t="n">
-        <v>0.628623608127862</v>
+        <v>0.628623608127855</v>
       </c>
       <c r="C36" s="32" t="n">
         <v>0.717702648139242</v>
@@ -36347,7 +36347,7 @@
         <v>0.119219168678356</v>
       </c>
       <c r="B37" s="33" t="n">
-        <v>0.632990663865204</v>
+        <v>0.632990663865196</v>
       </c>
       <c r="C37" s="32" t="n">
         <v>0.689073507275891</v>
@@ -36358,7 +36358,7 @@
         <v>0.138430537259882</v>
       </c>
       <c r="B38" s="33" t="n">
-        <v>0.637555960560158</v>
+        <v>0.63755596056015</v>
       </c>
       <c r="C38" s="32" t="n">
         <v>0.658377604891228</v>
@@ -36369,7 +36369,7 @@
         <v>0.160737688901019</v>
       </c>
       <c r="B39" s="33" t="n">
-        <v>0.642298428241314</v>
+        <v>0.642298428241305</v>
       </c>
       <c r="C39" s="32" t="n">
         <v>0.625635822348224</v>
@@ -36380,7 +36380,7 @@
         <v>0.186639488256384</v>
       </c>
       <c r="B40" s="33" t="n">
-        <v>0.647191056996101</v>
+        <v>0.647191056996092</v>
       </c>
       <c r="C40" s="32" t="n">
         <v>0.590911354884235</v>
@@ -36391,7 +36391,7 @@
         <v>0.216715188670254</v>
       </c>
       <c r="B41" s="33" t="n">
-        <v>0.652200610629809</v>
+        <v>0.6522006106298</v>
       </c>
       <c r="C41" s="32" t="n">
         <v>0.554317343579971</v>
@@ -36402,7 +36402,7 @@
         <v>0.251637386274163</v>
       </c>
       <c r="B42" s="33" t="n">
-        <v>0.657287535272701</v>
+        <v>0.657287535272691</v>
       </c>
       <c r="C42" s="32" t="n">
         <v>0.516024395032891</v>
@@ -36413,7 +36413,7 @@
         <v>0.292187061550354</v>
       </c>
       <c r="B43" s="33" t="n">
-        <v>0.662406126341922</v>
+        <v>0.662406126341912</v>
       </c>
       <c r="C43" s="32" t="n">
         <v>0.476267451699933</v>
@@ -36424,7 +36424,7 @@
         <v>0.339271044742195</v>
       </c>
       <c r="B44" s="33" t="n">
-        <v>0.667505020846813</v>
+        <v>0.667505020846802</v>
       </c>
       <c r="C44" s="32" t="n">
         <v>0.43535129547812</v>
@@ -36435,7 +36435,7 @@
         <v>0.39394229569821</v>
       </c>
       <c r="B45" s="33" t="n">
-        <v>0.672526269399698</v>
+        <v>0.672526269399687</v>
       </c>
       <c r="C45" s="32" t="n">
         <v>0.393653776011565</v>
@@ -36446,7 +36446,7 @@
         <v>0.45742345167682</v>
       </c>
       <c r="B46" s="33" t="n">
-        <v>0.677407197757734</v>
+        <v>0.677407197757721</v>
       </c>
       <c r="C46" s="32" t="n">
         <v>0.351625676310468</v>
@@ -36457,7 +36457,7 @@
         <v>0.531134169721718</v>
       </c>
       <c r="B47" s="33" t="n">
-        <v>0.682091104589113</v>
+        <v>0.682091104589101</v>
       </c>
       <c r="C47" s="32" t="n">
         <v>0.30978599872001</v>
@@ -36468,7 +36468,7 @@
         <v>0.616722875077448</v>
       </c>
       <c r="B48" s="33" t="n">
-        <v>0.686517700564339</v>
+        <v>0.686517700564326</v>
       </c>
       <c r="C48" s="32" t="n">
         <v>0.268711428375415</v>
@@ -36479,7 +36479,7 @@
         <v>0.716103625649</v>
       </c>
       <c r="B49" s="33" t="n">
-        <v>0.690630169934122</v>
+        <v>0.690630169934107</v>
       </c>
       <c r="C49" s="32" t="n">
         <v>0.229018880610733</v>
@@ -36490,7 +36490,7 @@
         <v>0.831498916921552</v>
       </c>
       <c r="B50" s="33" t="n">
-        <v>0.694378226245563</v>
+        <v>0.694378226245547</v>
       </c>
       <c r="C50" s="32" t="n">
         <v>0.191340446907739</v>
@@ -36501,7 +36501,7 @@
         <v>0.965489384605629</v>
       </c>
       <c r="B51" s="33" t="n">
-        <v>0.697721290897148</v>
+        <v>0.697721290897131</v>
       </c>
       <c r="C51" s="32" t="n">
         <v>0.156290801668999</v>
@@ -36512,7 +36512,7 @@
         <v>1.12107151652983</v>
       </c>
       <c r="B52" s="33" t="n">
-        <v>0.700631513410051</v>
+        <v>0.700631513410032</v>
       </c>
       <c r="C52" s="32" t="n">
         <v>0.124428269199496</v>
@@ -36523,7 +36523,7 @@
         <v>1.30172466441758</v>
       </c>
       <c r="B53" s="33" t="n">
-        <v>0.703096275551466</v>
+        <v>0.703096275551445</v>
       </c>
       <c r="C53" s="32" t="n">
         <v>0.0962122518494158</v>
@@ -36534,7 +36534,7 @@
         <v>1.51148885416176</v>
       </c>
       <c r="B54" s="33" t="n">
-        <v>0.705119775755431</v>
+        <v>0.705119775755408</v>
       </c>
       <c r="C54" s="32" t="n">
         <v>0.0719614310920637</v>
@@ -36545,7 +36545,7 @@
         <v>1.7550551347027</v>
       </c>
       <c r="B55" s="33" t="n">
-        <v>0.706723303297694</v>
+        <v>0.706723303297668</v>
       </c>
       <c r="C55" s="32" t="n">
         <v>0.0518187361468644</v>
@@ -36556,7 +36556,7 @@
         <v>2.03787048602125</v>
       </c>
       <c r="B56" s="33" t="n">
-        <v>0.707943910841903</v>
+        <v>0.707943910841873</v>
       </c>
       <c r="C56" s="32" t="n">
         <v>0.0357299947763476</v>
@@ -36567,7 +36567,7 @@
         <v>2.3662596323505</v>
       </c>
       <c r="B57" s="33" t="n">
-        <v>0.708831395746813</v>
+        <v>0.70883139574678</v>
       </c>
       <c r="C57" s="32" t="n">
         <v>0.0234427747208725</v>
@@ -36578,7 +36578,7 @@
         <v>2.74756648476882</v>
       </c>
       <c r="B58" s="33" t="n">
-        <v>0.709443795614982</v>
+        <v>0.709443795614946</v>
       </c>
       <c r="C58" s="32" t="n">
         <v>0.014529602043232</v>
@@ -36589,7 +36589,7 @@
         <v>3.19031837631699</v>
       </c>
       <c r="B59" s="33" t="n">
-        <v>0.709841942992282</v>
+        <v>0.70984194299224</v>
       </c>
       <c r="C59" s="32" t="n">
         <v>0.00843533133749581</v>
@@ -36600,7 +36600,7 @@
         <v>3.70441676250184</v>
       </c>
       <c r="B60" s="33" t="n">
-        <v>0.710083297814694</v>
+        <v>0.710083297814647</v>
       </c>
       <c r="C60" s="32" t="n">
         <v>0.00454257854678033</v>
@@ -36611,7 +36611,7 @@
         <v>4.30135865190564</v>
       </c>
       <c r="B61" s="33" t="n">
-        <v>0.710219381497255</v>
+        <v>0.710219381497201</v>
       </c>
       <c r="C61" s="32" t="n">
         <v>0.00224346329779067</v>
@@ -36622,7 +36622,7 @@
         <v>4.99449371885145</v>
       </c>
       <c r="B62" s="33" t="n">
-        <v>0.710290544777671</v>
+        <v>0.710290544777609</v>
       </c>
       <c r="C62" s="32" t="n">
         <v>0.00100281235501789</v>
@@ -36633,7 +36633,7 @@
         <v>5.79932284804829</v>
       </c>
       <c r="B63" s="33" t="n">
-        <v>0.710325323319857</v>
+        <v>0.710325323319787</v>
       </c>
       <c r="C63" s="32" t="n">
         <v>0.000399526279868014</v>
@@ -36644,7 +36644,7 @@
         <v>6.73384478770136</v>
       </c>
       <c r="B64" s="33" t="n">
-        <v>0.710342036594481</v>
+        <v>0.710342036594401</v>
       </c>
       <c r="C64" s="32" t="n">
         <v>0.000139366302125243</v>
@@ -36655,7 +36655,7 @@
         <v>7.81895866344345</v>
       </c>
       <c r="B65" s="33" t="n">
-        <v>0.710351105053317</v>
+        <v>0.710351105053224</v>
       </c>
       <c r="C65" s="32" t="n">
         <v>4.16930374467394E-005</v>
@@ -36666,7 +36666,7 @@
         <v>9.07893135468401</v>
       </c>
       <c r="B66" s="33" t="n">
-        <v>0.710357723165527</v>
+        <v>0.710357723165425</v>
       </c>
       <c r="C66" s="32" t="n">
         <v>1.04426230026579E-005</v>
@@ -36677,7 +36677,7 @@
         <v>10.5419401855188</v>
       </c>
       <c r="B67" s="33" t="n">
-        <v>0.710364153365868</v>
+        <v>0.71036415336576</v>
       </c>
       <c r="C67" s="32" t="n">
         <v>2.12934587029853E-006</v>
@@ -36688,7 +36688,7 @@
         <v>12.2407030666357</v>
       </c>
       <c r="B68" s="33" t="n">
-        <v>0.710371287349067</v>
+        <v>0.710371287348953</v>
       </c>
       <c r="C68" s="32" t="n">
         <v>3.42177809020532E-007</v>
@@ -36699,7 +36699,7 @@
         <v>14.2132101803583</v>
       </c>
       <c r="B69" s="33" t="n">
-        <v>0.710379500225859</v>
+        <v>0.71037950022576</v>
       </c>
       <c r="C69" s="32" t="n">
         <v>4.17267125514354E-008</v>
@@ -36710,7 +36710,7 @@
         <v>16.5035735718214</v>
       </c>
       <c r="B70" s="33" t="n">
-        <v>0.710389024882073</v>
+        <v>0.710389024882015</v>
       </c>
       <c r="C70" s="32" t="n">
         <v>3.69538746631243E-009</v>
@@ -36721,7 +36721,7 @@
         <v>19.1630136460597</v>
       </c>
       <c r="B71" s="33" t="n">
-        <v>0.710400082935264</v>
+        <v>0.710400082935245</v>
       </c>
       <c r="C71" s="32" t="n">
         <v>2.25852961254674E-010</v>
@@ -36732,7 +36732,7 @@
         <v>22.2510046324799</v>
       </c>
       <c r="B72" s="33" t="n">
-        <v>0.710412922809111</v>
+        <v>0.710412922809113</v>
       </c>
       <c r="C72" s="32" t="n">
         <v>8.97758658398466E-012</v>
@@ -36743,7 +36743,7 @@
         <v>25.8366046332408</v>
       </c>
       <c r="B73" s="33" t="n">
-        <v>0.710427832914435</v>
+        <v>0.710427832914446</v>
       </c>
       <c r="C73" s="32" t="n">
         <v>2.16642030482381E-013</v>
